--- a/question_bank/ENGLISH - Grammer.xlsx
+++ b/question_bank/ENGLISH - Grammer.xlsx
@@ -9,24 +9,22 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="5" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="2" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="Syllabus" sheetId="26" r:id="rId1"/>
-    <sheet name="Index" sheetId="14" r:id="rId2"/>
-    <sheet name="Convert to Abstarct Noun" sheetId="4" r:id="rId3"/>
-    <sheet name="Article" sheetId="20" r:id="rId4"/>
-    <sheet name="Preposition" sheetId="19" r:id="rId5"/>
-    <sheet name="Conjunction" sheetId="11" r:id="rId6"/>
-    <sheet name="Correct Sentences" sheetId="15" r:id="rId7"/>
-    <sheet name="Comparison of Adjectives" sheetId="23" r:id="rId8"/>
-    <sheet name="Formation of Adjectives" sheetId="25" r:id="rId9"/>
+    <sheet name="Convert to Abstarct Noun" sheetId="4" r:id="rId2"/>
+    <sheet name="Article" sheetId="20" r:id="rId3"/>
+    <sheet name="Preposition" sheetId="19" r:id="rId4"/>
+    <sheet name="Correct Sentences" sheetId="15" r:id="rId5"/>
+    <sheet name="Comparison of Adjectives" sheetId="23" r:id="rId6"/>
+    <sheet name="Formation of Adjectives" sheetId="25" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Comparison of Adjectives'!$A$1:$B$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Formation of Adjectives'!$A$1:$B$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Comparison of Adjectives'!$A$1:$B$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Formation of Adjectives'!$A$1:$B$85</definedName>
   </definedNames>
-  <calcPr calcId="162913" refMode="R1C1"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="823">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="800">
   <si>
     <t>Anger</t>
   </si>
@@ -230,33 +228,6 @@
     <t>silence</t>
   </si>
   <si>
-    <t>One Word Substitution</t>
-  </si>
-  <si>
-    <t>Antonyms</t>
-  </si>
-  <si>
-    <t>Synonyms</t>
-  </si>
-  <si>
-    <t>Direct - Indirec 1</t>
-  </si>
-  <si>
-    <t>Voice Change</t>
-  </si>
-  <si>
-    <t>Correct Spelling</t>
-  </si>
-  <si>
-    <t>Conjunction</t>
-  </si>
-  <si>
-    <t>Positive-Negative</t>
-  </si>
-  <si>
-    <t>Correct Sentences</t>
-  </si>
-  <si>
     <t>She resembles her father.</t>
   </si>
   <si>
@@ -2140,42 +2111,9 @@
     <t>Answers</t>
   </si>
   <si>
-    <t>One Word Substitution (MS)</t>
-  </si>
-  <si>
-    <t>Parts of Speech</t>
-  </si>
-  <si>
-    <t>Noun</t>
-  </si>
-  <si>
-    <t>Pronoun</t>
-  </si>
-  <si>
-    <t>Preposition</t>
-  </si>
-  <si>
-    <t>Verb</t>
-  </si>
-  <si>
-    <t>Adverb</t>
-  </si>
-  <si>
     <t>Adjective</t>
   </si>
   <si>
-    <t>Jumple Words</t>
-  </si>
-  <si>
-    <t>Vocabulary</t>
-  </si>
-  <si>
-    <t>Sentence Change</t>
-  </si>
-  <si>
-    <t>Subject Predicate</t>
-  </si>
-  <si>
     <t>Include</t>
   </si>
   <si>
@@ -2185,12 +2123,6 @@
     <t>Forget</t>
   </si>
   <si>
-    <t>Transformation of Sentences (Mixed)</t>
-  </si>
-  <si>
-    <t>Article</t>
-  </si>
-  <si>
     <t>___ child</t>
   </si>
   <si>
@@ -4894,9 +4826,6 @@
     <t>Old (বয়সে বড়, পুরাতন)</t>
   </si>
   <si>
-    <t>Comparison of Adjectives</t>
-  </si>
-  <si>
     <t>Comparative | Superlative</t>
   </si>
   <si>
@@ -5170,9 +5099,6 @@
     <t>trustful</t>
   </si>
   <si>
-    <t>Formation of Adjectives</t>
-  </si>
-  <si>
     <t>1.  Spellings Of Words</t>
   </si>
   <si>
@@ -5270,6 +5196,9 @@
   </si>
   <si>
     <t>Please write Comparative &amp; Superlative of following Adjectives</t>
+  </si>
+  <si>
+    <t>Syllabus</t>
   </si>
 </sst>
 </file>
@@ -5411,13 +5340,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -5748,140 +5675,226 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:A27"/>
+  <dimension ref="A1:B27"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="139.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="18" t="s">
+        <v>799</v>
+      </c>
+      <c r="B1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>766</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>767</v>
+      </c>
+      <c r="B3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>768</v>
+      </c>
+      <c r="B4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>769</v>
+      </c>
+      <c r="B5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>770</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>771</v>
+      </c>
+      <c r="B7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>772</v>
+      </c>
+      <c r="B8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>773</v>
+      </c>
+      <c r="B9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>774</v>
+      </c>
+      <c r="B10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>775</v>
+      </c>
+      <c r="B11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>776</v>
+      </c>
+      <c r="B12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>777</v>
+      </c>
+      <c r="B13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>778</v>
+      </c>
+      <c r="B14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>779</v>
+      </c>
+      <c r="B15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>780</v>
+      </c>
+      <c r="B16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>781</v>
+      </c>
+      <c r="B17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>782</v>
+      </c>
+      <c r="B18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="18" t="s">
+        <v>783</v>
+      </c>
+      <c r="B19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>784</v>
+      </c>
+      <c r="B20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>785</v>
+      </c>
+      <c r="B21">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>786</v>
+      </c>
+      <c r="B22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>787</v>
+      </c>
+      <c r="B23">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>788</v>
+      </c>
+      <c r="B24">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>789</v>
+      </c>
+      <c r="B25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="B26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>792</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>797</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>799</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>801</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>805</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="20" t="s">
-        <v>807</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>808</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>809</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>815</v>
+      <c r="B27">
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -5891,1218 +5904,1052 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:B31"/>
+  <dimension ref="A1:B135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="34.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="2" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B4" s="5" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="5" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B5" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B6" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B7" s="5"/>
-    </row>
-    <row r="8" spans="2:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="9" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B9" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B10" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B11" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B12" s="5" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B13" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="14" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B14" s="5" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="16" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B16" s="1" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B17" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B18" s="5" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B19" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B20" s="5" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B21" s="5" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B22" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B24" s="5" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="5" t="s">
-        <v>789</v>
-      </c>
-    </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B26" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B29" s="5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="5" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="5" t="s">
-        <v>210</v>
-      </c>
+    <row r="1" spans="1:2" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="23" t="s">
+        <v>793</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="15" t="s">
+        <v>299</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>301</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
+        <v>303</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="15" t="s">
+        <v>305</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="15" t="s">
+        <v>311</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="15" t="s">
+        <v>313</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="15" t="s">
+        <v>319</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="15" t="s">
+        <v>321</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="15" t="s">
+        <v>325</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="15" t="s">
+        <v>327</v>
+      </c>
+      <c r="B48" s="15" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="15" t="s">
+        <v>329</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="15" t="s">
+        <v>331</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="15" t="s">
+        <v>332</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="15" t="s">
+        <v>334</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="15" t="s">
+        <v>336</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="15" t="s">
+        <v>338</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="15" t="s">
+        <v>340</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="15" t="s">
+        <v>342</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="15" t="s">
+        <v>344</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B58" s="15" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="15" t="s">
+        <v>346</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="B60" s="15" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="15" t="s">
+        <v>349</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="15" t="s">
+        <v>351</v>
+      </c>
+      <c r="B62" s="15" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="15" t="s">
+        <v>353</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="15" t="s">
+        <v>355</v>
+      </c>
+      <c r="B64" s="15" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="15" t="s">
+        <v>357</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="15" t="s">
+        <v>359</v>
+      </c>
+      <c r="B66" s="15" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="15" t="s">
+        <v>361</v>
+      </c>
+      <c r="B67" s="15" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="15" t="s">
+        <v>363</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="15" t="s">
+        <v>365</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="15" t="s">
+        <v>367</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="15" t="s">
+        <v>369</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="15" t="s">
+        <v>289</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="15" t="s">
+        <v>372</v>
+      </c>
+      <c r="B73" s="15" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="15" t="s">
+        <v>374</v>
+      </c>
+      <c r="B74" s="15" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="15" t="s">
+        <v>376</v>
+      </c>
+      <c r="B75" s="15" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="15" t="s">
+        <v>378</v>
+      </c>
+      <c r="B76" s="15" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="15" t="s">
+        <v>380</v>
+      </c>
+      <c r="B77" s="15" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="15" t="s">
+        <v>382</v>
+      </c>
+      <c r="B78" s="15" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="15" t="s">
+        <v>383</v>
+      </c>
+      <c r="B79" s="15" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="15" t="s">
+        <v>385</v>
+      </c>
+      <c r="B80" s="15" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="15" t="s">
+        <v>387</v>
+      </c>
+      <c r="B81" s="15" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="15" t="s">
+        <v>389</v>
+      </c>
+      <c r="B82" s="15" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="15" t="s">
+        <v>391</v>
+      </c>
+      <c r="B83" s="15" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="15" t="s">
+        <v>393</v>
+      </c>
+      <c r="B84" s="15" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="15" t="s">
+        <v>395</v>
+      </c>
+      <c r="B85" s="15" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="15" t="s">
+        <v>397</v>
+      </c>
+      <c r="B86" s="15" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="15" t="s">
+        <v>398</v>
+      </c>
+      <c r="B87" s="15" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="15" t="s">
+        <v>400</v>
+      </c>
+      <c r="B88" s="15" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="15" t="s">
+        <v>402</v>
+      </c>
+      <c r="B89" s="15" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="15" t="s">
+        <v>404</v>
+      </c>
+      <c r="B90" s="15" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="15" t="s">
+        <v>405</v>
+      </c>
+      <c r="B91" s="15" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="B92" s="15" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="B93" s="15" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="15" t="s">
+        <v>411</v>
+      </c>
+      <c r="B94" s="15" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="15" t="s">
+        <v>413</v>
+      </c>
+      <c r="B95" s="15" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="15" t="s">
+        <v>470</v>
+      </c>
+      <c r="B96" s="15" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="15" t="s">
+        <v>415</v>
+      </c>
+      <c r="B97" s="15" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="15" t="s">
+        <v>418</v>
+      </c>
+      <c r="B98" s="15" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="15" t="s">
+        <v>419</v>
+      </c>
+      <c r="B99" s="15" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="15" t="s">
+        <v>420</v>
+      </c>
+      <c r="B100" s="15" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="15" t="s">
+        <v>422</v>
+      </c>
+      <c r="B101" s="15" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A102" s="15" t="s">
+        <v>424</v>
+      </c>
+      <c r="B102" s="15" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A103" s="15" t="s">
+        <v>426</v>
+      </c>
+      <c r="B103" s="15" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="15" t="s">
+        <v>429</v>
+      </c>
+      <c r="B104" s="15" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="15" t="s">
+        <v>430</v>
+      </c>
+      <c r="B105" s="15" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="15" t="s">
+        <v>432</v>
+      </c>
+      <c r="B106" s="15" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="B107" s="15" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="15" t="s">
+        <v>473</v>
+      </c>
+      <c r="B108" s="15" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="15" t="s">
+        <v>434</v>
+      </c>
+      <c r="B109" s="15" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="15" t="s">
+        <v>435</v>
+      </c>
+      <c r="B110" s="15" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="B111" s="15" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="B112" s="15" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="15" t="s">
+        <v>438</v>
+      </c>
+      <c r="B113" s="15" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="B114" s="15" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="15" t="s">
+        <v>474</v>
+      </c>
+      <c r="B115" s="15" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="B116" s="15" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A117" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="B117" s="15" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="B118" s="15" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="B119" s="15" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="B120" s="15" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="15" t="s">
+        <v>445</v>
+      </c>
+      <c r="B121" s="15" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="15" t="s">
+        <v>446</v>
+      </c>
+      <c r="B122" s="15" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="15" t="s">
+        <v>447</v>
+      </c>
+      <c r="B123" s="15" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124"/>
+      <c r="B124"/>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125"/>
+      <c r="B125"/>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126"/>
+      <c r="B126"/>
+    </row>
+    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A127"/>
+      <c r="B127"/>
+    </row>
+    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A128"/>
+      <c r="B128"/>
+    </row>
+    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A129"/>
+      <c r="B129"/>
+    </row>
+    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A130"/>
+      <c r="B130"/>
+    </row>
+    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A131"/>
+      <c r="B131"/>
+    </row>
+    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A132"/>
+      <c r="B132"/>
+    </row>
+    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A133"/>
+      <c r="B133"/>
+    </row>
+    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A134"/>
+      <c r="B134"/>
+    </row>
+    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A135"/>
+      <c r="B135"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B29" location="'Correct Spelling'!A1" display="Correct Spelling"/>
-    <hyperlink ref="B30" location="'Correct Sentences'!A1" display="Correct Sentences"/>
-    <hyperlink ref="B3" location="'One Word Subs'!A1" display="One Word Substitution"/>
-    <hyperlink ref="B4" location="'One Word Subs (MS)'!A1" display="One Word Substitution (MS)"/>
-    <hyperlink ref="B5" location="Antonyms!A1" display="Antonyms"/>
-    <hyperlink ref="B6" location="Synonyms!A1" display="Synonyms"/>
-    <hyperlink ref="B9" location="'Direct - Indirect 1'!A1" display="Direct - Indirec 1"/>
-    <hyperlink ref="B10" location="'Direct - Indirect 2'!A1" display="Direct - Indirec 1"/>
-    <hyperlink ref="B11" location="'Direct-Indirect 3'!A1" display="Direct - Indirec 1"/>
-    <hyperlink ref="B12" location="'Voice Change'!A1" display="Voice Change"/>
-    <hyperlink ref="B31" location="'Jumble Words'!A1" display="Jumple Words"/>
-    <hyperlink ref="B13" location="'Positive-Negative'!A1" display="Positive-Negative"/>
-    <hyperlink ref="B14" location="'Transformation of Sentences'!A1" display="Transformation of Sentences (Mixed)"/>
-    <hyperlink ref="B20" location="Article!A1" display="Article"/>
-    <hyperlink ref="B21" location="Preposition!A1" display="Preposition"/>
-    <hyperlink ref="B18" location="'Convert to Abstarct Noun'!A1" display="Noun"/>
-    <hyperlink ref="B24" location="'Comparison of Adjectives'!A1" display="Comparison of Adjectives"/>
-    <hyperlink ref="B25" location="'Formation of Adjectives'!A1" display="Formation of Adjectives"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B135"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="17.7109375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="19.42578125" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="22" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
-        <v>817</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B7" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
-        <v>315</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>318</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="17" t="s">
-        <v>325</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
-        <v>327</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
-        <v>329</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
-        <v>331</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="s">
-        <v>333</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
-        <v>335</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
-        <v>338</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
-        <v>313</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="17" t="s">
-        <v>314</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="17" t="s">
-        <v>341</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
-        <v>343</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
-        <v>345</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="17" t="s">
-        <v>347</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="17" t="s">
-        <v>351</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
-        <v>353</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="17" t="s">
-        <v>354</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="17" t="s">
-        <v>356</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="17" t="s">
-        <v>358</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="17" t="s">
-        <v>360</v>
-      </c>
-      <c r="B54" s="17" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="17" t="s">
-        <v>362</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="17" t="s">
-        <v>364</v>
-      </c>
-      <c r="B56" s="17" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="17" t="s">
-        <v>366</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>367</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="17" t="s">
-        <v>14</v>
-      </c>
-      <c r="B58" s="17" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="17" t="s">
-        <v>368</v>
-      </c>
-      <c r="B59" s="17" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
-        <v>310</v>
-      </c>
-      <c r="B60" s="17" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="17" t="s">
-        <v>371</v>
-      </c>
-      <c r="B61" s="17" t="s">
-        <v>372</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="17" t="s">
-        <v>373</v>
-      </c>
-      <c r="B62" s="17" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="17" t="s">
-        <v>375</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="17" t="s">
-        <v>377</v>
-      </c>
-      <c r="B64" s="17" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="B65" s="17" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="B66" s="17" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="17" t="s">
-        <v>383</v>
-      </c>
-      <c r="B67" s="17" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="17" t="s">
-        <v>385</v>
-      </c>
-      <c r="B68" s="17" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="17" t="s">
-        <v>387</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="17" t="s">
-        <v>389</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="17" t="s">
-        <v>391</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="17" t="s">
-        <v>311</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="17" t="s">
-        <v>394</v>
-      </c>
-      <c r="B73" s="17" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="17" t="s">
-        <v>396</v>
-      </c>
-      <c r="B74" s="17" t="s">
-        <v>397</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="17" t="s">
-        <v>398</v>
-      </c>
-      <c r="B75" s="17" t="s">
-        <v>399</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="17" t="s">
-        <v>400</v>
-      </c>
-      <c r="B76" s="17" t="s">
-        <v>401</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="17" t="s">
-        <v>402</v>
-      </c>
-      <c r="B77" s="17" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="17" t="s">
-        <v>404</v>
-      </c>
-      <c r="B78" s="17" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="17" t="s">
-        <v>405</v>
-      </c>
-      <c r="B79" s="17" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="17" t="s">
-        <v>407</v>
-      </c>
-      <c r="B80" s="17" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="17" t="s">
-        <v>409</v>
-      </c>
-      <c r="B81" s="17" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="17" t="s">
-        <v>411</v>
-      </c>
-      <c r="B82" s="17" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="17" t="s">
-        <v>413</v>
-      </c>
-      <c r="B83" s="17" t="s">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="17" t="s">
-        <v>415</v>
-      </c>
-      <c r="B84" s="17" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="17" t="s">
-        <v>417</v>
-      </c>
-      <c r="B85" s="17" t="s">
-        <v>418</v>
-      </c>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A86" s="17" t="s">
-        <v>419</v>
-      </c>
-      <c r="B86" s="17" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A87" s="17" t="s">
-        <v>420</v>
-      </c>
-      <c r="B87" s="17" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A88" s="17" t="s">
-        <v>422</v>
-      </c>
-      <c r="B88" s="17" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A89" s="17" t="s">
-        <v>424</v>
-      </c>
-      <c r="B89" s="17" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A90" s="17" t="s">
-        <v>426</v>
-      </c>
-      <c r="B90" s="17" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A91" s="17" t="s">
-        <v>427</v>
-      </c>
-      <c r="B91" s="17" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A92" s="17" t="s">
-        <v>429</v>
-      </c>
-      <c r="B92" s="17" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A93" s="17" t="s">
-        <v>431</v>
-      </c>
-      <c r="B93" s="17" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A94" s="17" t="s">
-        <v>433</v>
-      </c>
-      <c r="B94" s="17" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A95" s="17" t="s">
-        <v>435</v>
-      </c>
-      <c r="B95" s="17" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A96" s="17" t="s">
-        <v>492</v>
-      </c>
-      <c r="B96" s="17" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A97" s="17" t="s">
-        <v>437</v>
-      </c>
-      <c r="B97" s="17" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A98" s="17" t="s">
-        <v>440</v>
-      </c>
-      <c r="B98" s="17" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A99" s="17" t="s">
-        <v>441</v>
-      </c>
-      <c r="B99" s="17" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A100" s="17" t="s">
-        <v>442</v>
-      </c>
-      <c r="B100" s="17" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A101" s="17" t="s">
-        <v>444</v>
-      </c>
-      <c r="B101" s="17" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A102" s="17" t="s">
-        <v>446</v>
-      </c>
-      <c r="B102" s="17" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A103" s="17" t="s">
-        <v>448</v>
-      </c>
-      <c r="B103" s="17" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A104" s="17" t="s">
-        <v>451</v>
-      </c>
-      <c r="B104" s="17" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A105" s="17" t="s">
-        <v>452</v>
-      </c>
-      <c r="B105" s="17" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A106" s="17" t="s">
-        <v>454</v>
-      </c>
-      <c r="B106" s="17" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A107" s="17" t="s">
-        <v>312</v>
-      </c>
-      <c r="B107" s="17" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A108" s="17" t="s">
-        <v>495</v>
-      </c>
-      <c r="B108" s="17" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A109" s="17" t="s">
-        <v>456</v>
-      </c>
-      <c r="B109" s="17" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A110" s="17" t="s">
-        <v>457</v>
-      </c>
-      <c r="B110" s="17" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A111" s="17" t="s">
-        <v>458</v>
-      </c>
-      <c r="B111" s="17" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A112" s="17" t="s">
-        <v>459</v>
-      </c>
-      <c r="B112" s="17" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A113" s="17" t="s">
-        <v>460</v>
-      </c>
-      <c r="B113" s="17" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A114" s="17" t="s">
-        <v>461</v>
-      </c>
-      <c r="B114" s="17" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A115" s="17" t="s">
-        <v>496</v>
-      </c>
-      <c r="B115" s="17" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A116" s="17" t="s">
-        <v>462</v>
-      </c>
-      <c r="B116" s="17" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A117" s="17" t="s">
-        <v>463</v>
-      </c>
-      <c r="B117" s="17" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A118" s="17" t="s">
-        <v>464</v>
-      </c>
-      <c r="B118" s="17" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A119" s="17" t="s">
-        <v>465</v>
-      </c>
-      <c r="B119" s="17" t="s">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A120" s="17" t="s">
-        <v>466</v>
-      </c>
-      <c r="B120" s="17" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A121" s="17" t="s">
-        <v>467</v>
-      </c>
-      <c r="B121" s="17" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A122" s="17" t="s">
-        <v>468</v>
-      </c>
-      <c r="B122" s="17" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A123" s="17" t="s">
-        <v>469</v>
-      </c>
-      <c r="B123" s="17" t="s">
-        <v>486</v>
-      </c>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A124"/>
-      <c r="B124"/>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A125"/>
-      <c r="B125"/>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A126"/>
-      <c r="B126"/>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A127"/>
-      <c r="B127"/>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A128"/>
-      <c r="B128"/>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A129"/>
-      <c r="B129"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A130"/>
-      <c r="B130"/>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A131"/>
-      <c r="B131"/>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A132"/>
-      <c r="B132"/>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A133"/>
-      <c r="B133"/>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A134"/>
-      <c r="B134"/>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A135"/>
-      <c r="B135"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7111,148 +6958,397 @@
     <col min="2" max="2" width="165" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="22" customFormat="1" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>818</v>
-      </c>
-      <c r="B1" s="22" t="s">
+    <row r="1" spans="1:2" s="20" customFormat="1" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>794</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A2" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="B2" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>201</v>
       </c>
+      <c r="B6" s="5" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Index!A1" display="Questions"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B7" s="8" t="s">
         <v>264</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
+    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B8" s="8" t="s">
         <v>265</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B9" s="8" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B10" s="8" t="s">
         <v>267</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
+    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B11" s="8" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
+    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B12" s="8" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
+    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B13" s="8" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
+    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B14" s="8" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
+    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>227</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B15" s="8" t="s">
         <v>272</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
+    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B16" s="8" t="s">
         <v>273</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
+    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>229</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B17" s="8" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
+    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B18" s="8" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
+    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B19" s="8" t="s">
         <v>276</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B20" s="8" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B21" s="8" t="s">
         <v>278</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
+    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B22" s="8" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
+    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="B18" s="11" t="s">
+      <c r="B23" s="8" t="s">
         <v>280</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -7265,789 +7361,531 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="52.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19" customWidth="1"/>
+    <col min="1" max="2" width="50.7109375" style="7" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>819</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="B3" s="10" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>240</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="B7" s="10" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="B9" s="10" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>244</v>
-      </c>
-      <c r="B10" s="10" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A11" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="B11" s="10" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="B13" s="10" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="B14" s="10" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
-        <v>249</v>
-      </c>
-      <c r="B15" s="10" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="B16" s="10" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="6" t="s">
-        <v>251</v>
-      </c>
-      <c r="B17" s="10" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A18" s="6" t="s">
-        <v>252</v>
-      </c>
-      <c r="B18" s="10" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A19" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="B19" s="10" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A20" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A21" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="B21" s="10" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A22" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A23" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="B23" s="10" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A24" s="6" t="s">
-        <v>258</v>
-      </c>
-      <c r="B24" s="10" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="B25" s="10" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A26" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="B26" s="10" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A27" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="B27" s="10" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="B28" s="10" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="B29" s="10" t="s">
-        <v>308</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Index!A1" display="Questions"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B65"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="2" width="50.7109375" style="9" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="3"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
-        <v>820</v>
-      </c>
-      <c r="B1" s="12" t="s">
+      <c r="A1" s="13" t="s">
+        <v>796</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
+      <c r="A2" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>65</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A6" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A7" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A8" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A9" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A11" s="11" t="s">
         <v>73</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B11" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" s="6" customFormat="1" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="12" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A6" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A7" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A8" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A11" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A12" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B14" s="13" t="s">
+      <c r="B24" s="12" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="15" spans="1:2" s="8" customFormat="1" ht="90.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
+    <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="B16" s="14" t="s">
+      <c r="B25" s="12" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
+    <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A26" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="B17" s="14" t="s">
+      <c r="B26" s="12" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
+    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B27" s="12" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
+    <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="B19" s="14" t="s">
+      <c r="B28" s="12" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
+    <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="B20" s="14" t="s">
+      <c r="B29" s="12" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
+    <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A30" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="B21" s="14" t="s">
+      <c r="B30" s="12" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
+    <row r="31" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A31" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="B22" s="14" t="s">
+      <c r="B31" s="12" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="23" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
+    <row r="32" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A32" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B32" s="12" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="24" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
+    <row r="33" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A33" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="B24" s="14" t="s">
+      <c r="B33" s="12" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
+    <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="B25" s="14" t="s">
+      <c r="B34" s="12" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="26" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
+    <row r="35" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A35" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B35" s="12" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="27" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
+    <row r="36" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B27" s="14" t="s">
+      <c r="B36" s="12" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="28" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
+    <row r="37" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A37" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B28" s="14" t="s">
+      <c r="B37" s="12" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="29" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
+    <row r="38" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A38" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B29" s="14" t="s">
+      <c r="B38" s="12" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="30" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
+    <row r="39" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A39" s="12" t="s">
         <v>102</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B39" s="12" t="s">
         <v>165</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
+    <row r="40" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A40" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B31" s="14" t="s">
+      <c r="B40" s="12" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="32" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+    <row r="41" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B41" s="12" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="33" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
+    <row r="42" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="B33" s="14" t="s">
+      <c r="B42" s="12" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
+    <row r="43" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A43" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B34" s="14" t="s">
+      <c r="B43" s="12" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="35" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
+    <row r="44" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A44" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B35" s="14" t="s">
+      <c r="B44" s="12" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="36" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
+    <row r="45" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A45" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="14" t="s">
+      <c r="B45" s="12" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="37" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
+    <row r="46" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A46" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="B46" s="12" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="38" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
+    <row r="47" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A47" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="B47" s="12" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="39" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
+    <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A48" s="12" t="s">
         <v>111</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="B48" s="12" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="40" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
+    <row r="49" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A49" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="B49" s="12" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="41" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
+    <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A50" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="B50" s="12" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="42" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
+    <row r="51" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B42" s="14" t="s">
+      <c r="B51" s="12" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="43" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
+    <row r="52" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A52" s="12" t="s">
         <v>115</v>
       </c>
-      <c r="B43" s="14" t="s">
+      <c r="B52" s="12" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="44" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
+    <row r="53" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A53" s="12" t="s">
         <v>116</v>
       </c>
-      <c r="B44" s="14" t="s">
+      <c r="B53" s="12" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="45" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
+    <row r="54" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A54" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B45" s="14" t="s">
+      <c r="B54" s="12" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="46" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
+    <row r="55" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A55" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="B46" s="14" t="s">
+      <c r="B55" s="12" t="s">
         <v>181</v>
       </c>
     </row>
-    <row r="47" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
+    <row r="56" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A56" s="12" t="s">
         <v>119</v>
       </c>
-      <c r="B47" s="14" t="s">
+      <c r="B56" s="12" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="48" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
+    <row r="57" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A57" s="12" t="s">
         <v>120</v>
       </c>
-      <c r="B48" s="14" t="s">
+      <c r="B57" s="12" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="49" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
+    <row r="58" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A58" s="12" t="s">
         <v>121</v>
       </c>
-      <c r="B49" s="14" t="s">
+      <c r="B58" s="12" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="50" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="B50" s="14" t="s">
+      <c r="B59" s="12" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="51" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
+    <row r="60" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A60" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="B51" s="14" t="s">
+      <c r="B60" s="12" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="52" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
+    <row r="61" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A61" s="12" t="s">
         <v>124</v>
       </c>
-      <c r="B52" s="14" t="s">
+      <c r="B61" s="12" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="53" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
+    <row r="62" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A62" s="12" t="s">
         <v>125</v>
       </c>
-      <c r="B53" s="14" t="s">
+      <c r="B62" s="12" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="54" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
+    <row r="63" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A63" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="B54" s="14" t="s">
+      <c r="B63" s="12" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="55" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A55" s="14" t="s">
+    <row r="64" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A64" s="12" t="s">
         <v>127</v>
       </c>
-      <c r="B55" s="14" t="s">
+      <c r="B64" s="12" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="56" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
+    <row r="65" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A65" s="12" t="s">
         <v>128</v>
       </c>
-      <c r="B56" s="14" t="s">
+      <c r="B65" s="12" t="s">
         <v>191</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A57" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="60" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="B62" s="14" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A63" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A64" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B65" s="14" t="s">
-        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -8058,574 +7896,574 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.5703125" style="16" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49" style="16" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="16"/>
+    <col min="1" max="1" width="27.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="14"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>822</v>
+      <c r="A1" s="19" t="s">
+        <v>798</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>674</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>614</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>615</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>616</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>797</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>617</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>618</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>619</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>620</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>622</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>623</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>624</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>625</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>626</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>627</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="B24" s="14" t="s">
         <v>698</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="16" t="s">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
         <v>630</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="16" t="s">
+      <c r="B26" s="14" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
         <v>631</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
-        <v>696</v>
-      </c>
-      <c r="B4" s="16" t="s">
+      <c r="B27" s="14" t="s">
         <v>701</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="16" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
         <v>632</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B28" s="14" t="s">
         <v>702</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
         <v>633</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B29" s="14" t="s">
         <v>703</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
         <v>634</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B30" s="14" t="s">
         <v>704</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="16" t="s">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
         <v>635</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B31" s="14" t="s">
         <v>705</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="16" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
         <v>636</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B32" s="14" t="s">
         <v>706</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="16" t="s">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
         <v>637</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B33" s="14" t="s">
         <v>707</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="16" t="s">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
         <v>638</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B34" s="14" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
-        <v>821</v>
-      </c>
-      <c r="B12" s="16" t="s">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>639</v>
+      </c>
+      <c r="B35" s="14" t="s">
         <v>709</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
-        <v>639</v>
-      </c>
-      <c r="B13" s="16" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="B36" s="14" t="s">
         <v>710</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
-        <v>640</v>
-      </c>
-      <c r="B14" s="16" t="s">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>641</v>
+      </c>
+      <c r="B37" s="14" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="16" t="s">
-        <v>641</v>
-      </c>
-      <c r="B15" s="16" t="s">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>642</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>712</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="16" t="s">
-        <v>642</v>
-      </c>
-      <c r="B16" s="16" t="s">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>643</v>
+      </c>
+      <c r="B39" s="14" t="s">
         <v>713</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="16" t="s">
-        <v>643</v>
-      </c>
-      <c r="B17" s="16" t="s">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>644</v>
+      </c>
+      <c r="B40" s="14" t="s">
         <v>714</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="16" t="s">
-        <v>644</v>
-      </c>
-      <c r="B18" s="16" t="s">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="16" t="s">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
         <v>645</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B42" s="14" t="s">
         <v>716</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="16" t="s">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
         <v>646</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B43" s="14" t="s">
         <v>717</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="16" t="s">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
         <v>647</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B44" s="14" t="s">
         <v>718</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="16" t="s">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
         <v>648</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B45" s="14" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="16" t="s">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
         <v>649</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B46" s="14" t="s">
         <v>720</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
         <v>650</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B47" s="14" t="s">
         <v>721</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="16" t="s">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
         <v>651</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B48" s="14" t="s">
         <v>722</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="16" t="s">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
         <v>652</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B49" s="14" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="16" t="s">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
         <v>653</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B50" s="14" t="s">
         <v>724</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="16" t="s">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="14" t="s">
         <v>654</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B51" s="14" t="s">
         <v>725</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="16" t="s">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
         <v>655</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B52" s="14" t="s">
         <v>726</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="16" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="14" t="s">
         <v>656</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B53" s="14" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="16" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="14" t="s">
         <v>657</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B54" s="14" t="s">
         <v>728</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="16" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="14" t="s">
         <v>658</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B55" s="14" t="s">
         <v>729</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="16" t="s">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="14" t="s">
         <v>659</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B56" s="14" t="s">
         <v>730</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="16" t="s">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="14" t="s">
         <v>660</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B57" s="14" t="s">
         <v>731</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="16" t="s">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="14" t="s">
         <v>661</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B58" s="14" t="s">
         <v>732</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="14" t="s">
         <v>662</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B59" s="14" t="s">
         <v>733</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="14" t="s">
         <v>663</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B60" s="14" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="14" t="s">
+        <v>669</v>
+      </c>
+      <c r="B61" s="14" t="s">
         <v>734</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="16" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="14" t="s">
+        <v>673</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="14" t="s">
+        <v>671</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="14" t="s">
         <v>664</v>
       </c>
-      <c r="B38" s="16" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="16" t="s">
+      <c r="B66" s="14" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="14" t="s">
         <v>665</v>
       </c>
-      <c r="B39" s="16" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="16" t="s">
+      <c r="B67" s="14" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="14" t="s">
         <v>666</v>
       </c>
-      <c r="B40" s="16" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="16" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="16" t="s">
+      <c r="B68" s="14" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="14" t="s">
         <v>667</v>
       </c>
-      <c r="B42" s="16" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="16" t="s">
+      <c r="B69" s="14" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="14" t="s">
         <v>668</v>
       </c>
-      <c r="B43" s="16" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="16" t="s">
-        <v>669</v>
-      </c>
-      <c r="B44" s="16" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="16" t="s">
-        <v>670</v>
-      </c>
-      <c r="B45" s="16" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="16" t="s">
-        <v>671</v>
-      </c>
-      <c r="B46" s="16" t="s">
+      <c r="B70" s="14" t="s">
         <v>743</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="16" t="s">
-        <v>672</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="16" t="s">
-        <v>673</v>
-      </c>
-      <c r="B48" s="16" t="s">
-        <v>745</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="16" t="s">
-        <v>674</v>
-      </c>
-      <c r="B49" s="16" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="16" t="s">
-        <v>675</v>
-      </c>
-      <c r="B50" s="16" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="16" t="s">
-        <v>676</v>
-      </c>
-      <c r="B51" s="16" t="s">
-        <v>748</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="16" t="s">
-        <v>677</v>
-      </c>
-      <c r="B52" s="16" t="s">
-        <v>749</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="16" t="s">
-        <v>678</v>
-      </c>
-      <c r="B53" s="16" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="16" t="s">
-        <v>679</v>
-      </c>
-      <c r="B54" s="16" t="s">
-        <v>751</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="16" t="s">
-        <v>680</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>752</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="16" t="s">
-        <v>681</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="16" t="s">
-        <v>682</v>
-      </c>
-      <c r="B57" s="16" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="16" t="s">
-        <v>683</v>
-      </c>
-      <c r="B58" s="16" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="16" t="s">
-        <v>684</v>
-      </c>
-      <c r="B59" s="16" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="16" t="s">
-        <v>685</v>
-      </c>
-      <c r="B60" s="16" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="16" t="s">
-        <v>691</v>
-      </c>
-      <c r="B61" s="16" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="16" t="s">
-        <v>692</v>
-      </c>
-      <c r="B62" s="16" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="16" t="s">
-        <v>695</v>
-      </c>
-      <c r="B63" s="16" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="16" t="s">
-        <v>693</v>
-      </c>
-      <c r="B64" s="16" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="16" t="s">
-        <v>694</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>761</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="16" t="s">
-        <v>686</v>
-      </c>
-      <c r="B66" s="16" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="16" t="s">
-        <v>687</v>
-      </c>
-      <c r="B67" s="16" t="s">
-        <v>763</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="16" t="s">
-        <v>688</v>
-      </c>
-      <c r="B68" s="16" t="s">
-        <v>764</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="16" t="s">
-        <v>689</v>
-      </c>
-      <c r="B69" s="16" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="16" t="s">
-        <v>690</v>
-      </c>
-      <c r="B70" s="16" t="s">
-        <v>766</v>
       </c>
     </row>
   </sheetData>
@@ -8637,694 +8475,694 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" style="19" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" style="19" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="19"/>
+    <col min="1" max="1" width="22.7109375" style="17" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="17"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="24" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="23" t="s">
-        <v>816</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>209</v>
+    <row r="1" spans="1:2" s="22" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>792</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
-        <v>768</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>769</v>
+      <c r="A2" s="17" t="s">
+        <v>745</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>746</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
-        <v>770</v>
-      </c>
-      <c r="B3" s="19" t="s">
+      <c r="A3" s="17" t="s">
+        <v>747</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>748</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>749</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>761</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>762</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>751</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>752</v>
+      </c>
+      <c r="B18" s="17" t="s">
         <v>497</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="19" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
         <v>498</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B19" s="17" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>753</v>
+      </c>
+      <c r="B20" s="17" t="s">
         <v>500</v>
       </c>
-      <c r="B5" s="19" t="s">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="17" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>771</v>
-      </c>
-      <c r="B6" s="19" t="s">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="B22" s="17" t="s">
         <v>502</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
-        <v>772</v>
-      </c>
-      <c r="B7" s="19" t="s">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
         <v>503</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="19" t="s">
+      <c r="B23" s="17" t="s">
         <v>504</v>
       </c>
-      <c r="B8" s="19" t="s">
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
         <v>505</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="19" t="s">
+      <c r="B24" s="17" t="s">
         <v>506</v>
       </c>
-      <c r="B9" s="19" t="s">
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
         <v>507</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="19" t="s">
+      <c r="B25" s="17" t="s">
         <v>508</v>
       </c>
-      <c r="B10" s="19" t="s">
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
         <v>509</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="19" t="s">
+      <c r="B26" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="B11" s="19" t="s">
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
         <v>511</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="19" t="s">
+      <c r="B27" s="17" t="s">
         <v>512</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
         <v>513</v>
       </c>
-      <c r="B13" s="19" t="s">
-        <v>773</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="19" t="s">
-        <v>784</v>
-      </c>
-      <c r="B14" s="19" t="s">
+      <c r="B28" s="17" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
         <v>515</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B29" s="17" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
-        <v>785</v>
-      </c>
-      <c r="B16" s="19" t="s">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
         <v>517</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="19" t="s">
-        <v>774</v>
-      </c>
-      <c r="B17" s="19" t="s">
+      <c r="B31" s="17" t="s">
         <v>518</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>775</v>
-      </c>
-      <c r="B18" s="19" t="s">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
         <v>519</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="19" t="s">
+      <c r="B33" s="17" t="s">
         <v>520</v>
       </c>
-      <c r="B19" s="19" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
-        <v>776</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="19" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="19" t="s">
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="17" t="s">
+        <v>525</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="17" t="s">
         <v>523</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="19" t="s">
-        <v>777</v>
-      </c>
-      <c r="B22" s="19" t="s">
+      <c r="B35" s="17" t="s">
         <v>524</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="19" t="s">
-        <v>525</v>
-      </c>
-      <c r="B23" s="19" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="17" t="s">
+        <v>533</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="17" t="s">
+        <v>763</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="17" t="s">
+        <v>756</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="17" t="s">
+        <v>531</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="17" t="s">
+        <v>764</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="17" t="s">
+        <v>759</v>
+      </c>
+      <c r="B45" s="17" t="s">
         <v>527</v>
       </c>
-      <c r="B24" s="19" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
-        <v>529</v>
-      </c>
-      <c r="B25" s="19" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="19" t="s">
-        <v>531</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="19" t="s">
-        <v>533</v>
-      </c>
-      <c r="B27" s="19" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="19" t="s">
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="17" t="s">
+        <v>548</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="17" t="s">
+        <v>551</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="17" t="s">
+        <v>554</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="17" t="s">
+        <v>556</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="17" t="s">
+        <v>562</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="17" t="s">
+        <v>565</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="17" t="s">
+        <v>568</v>
+      </c>
+      <c r="B62" s="17" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="17" t="s">
+        <v>570</v>
+      </c>
+      <c r="B63" s="17" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="17" t="s">
+        <v>571</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="B66" s="17" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B67" s="17" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="17" t="s">
+        <v>580</v>
+      </c>
+      <c r="B69" s="17" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="17" t="s">
+        <v>581</v>
+      </c>
+      <c r="B70" s="17" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="17" t="s">
+        <v>583</v>
+      </c>
+      <c r="B71" s="17" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="17" t="s">
+        <v>584</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="17" t="s">
+        <v>586</v>
+      </c>
+      <c r="B73" s="17" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="17" t="s">
         <v>535</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B74" s="17" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="19" t="s">
-        <v>537</v>
-      </c>
-      <c r="B29" s="19" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="19" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="19" t="s">
-        <v>539</v>
-      </c>
-      <c r="B31" s="19" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="19" t="s">
-        <v>543</v>
-      </c>
-      <c r="B32" s="19" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="19" t="s">
-        <v>541</v>
-      </c>
-      <c r="B33" s="19" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="19" t="s">
-        <v>547</v>
-      </c>
-      <c r="B34" s="19" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="19" t="s">
-        <v>545</v>
-      </c>
-      <c r="B35" s="19" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="19" t="s">
-        <v>550</v>
-      </c>
-      <c r="B36" s="19" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="19" t="s">
-        <v>555</v>
-      </c>
-      <c r="B37" s="19" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="19" t="s">
-        <v>786</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
-        <v>779</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>780</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="19" t="s">
-        <v>553</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="19" t="s">
-        <v>787</v>
-      </c>
-      <c r="B41" s="19" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="19" t="s">
-        <v>557</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="19" t="s">
-        <v>215</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="19" t="s">
-        <v>559</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="19" t="s">
-        <v>782</v>
-      </c>
-      <c r="B45" s="19" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="19" t="s">
-        <v>561</v>
-      </c>
-      <c r="B46" s="19" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="19" t="s">
-        <v>563</v>
-      </c>
-      <c r="B47" s="19" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="19" t="s">
-        <v>565</v>
-      </c>
-      <c r="B48" s="19" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="19" t="s">
-        <v>567</v>
-      </c>
-      <c r="B49" s="19" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="19" t="s">
-        <v>568</v>
-      </c>
-      <c r="B50" s="19" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
-        <v>570</v>
-      </c>
-      <c r="B51" s="19" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="19" t="s">
-        <v>571</v>
-      </c>
-      <c r="B52" s="19" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="19" t="s">
-        <v>573</v>
-      </c>
-      <c r="B53" s="19" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="19" t="s">
-        <v>574</v>
-      </c>
-      <c r="B54" s="19" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B55" s="19" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="19" t="s">
-        <v>576</v>
-      </c>
-      <c r="B56" s="19" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="19" t="s">
-        <v>578</v>
-      </c>
-      <c r="B57" s="19" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="19" t="s">
-        <v>584</v>
-      </c>
-      <c r="B58" s="19" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B59" s="19" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="19" t="s">
-        <v>587</v>
-      </c>
-      <c r="B60" s="19" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="19" t="s">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="17" t="s">
         <v>588</v>
       </c>
-      <c r="B61" s="19" t="s">
+      <c r="B75" s="17" t="s">
         <v>589</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="19" t="s">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B76" s="17" t="s">
         <v>590</v>
       </c>
-      <c r="B62" s="19" t="s">
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B77" s="17" t="s">
         <v>591</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="19" t="s">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="17" t="s">
         <v>592</v>
       </c>
-      <c r="B63" s="19" t="s">
+      <c r="B78" s="17" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="17" t="s">
         <v>596</v>
       </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="19" t="s">
-        <v>593</v>
-      </c>
-      <c r="B64" s="19" t="s">
+      <c r="B79" s="17" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="17" t="s">
+        <v>604</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="17" t="s">
         <v>594</v>
       </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="19" t="s">
+      <c r="B82" s="17" t="s">
         <v>595</v>
       </c>
-      <c r="B65" s="19" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="19" t="s">
-        <v>214</v>
-      </c>
-      <c r="B66" s="19" t="s">
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="17" t="s">
         <v>598</v>
       </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="19" t="s">
-        <v>216</v>
-      </c>
-      <c r="B67" s="19" t="s">
+      <c r="B83" s="17" t="s">
         <v>599</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="19" t="s">
-        <v>600</v>
-      </c>
-      <c r="B68" s="19" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="19" t="s">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="17" t="s">
         <v>602</v>
       </c>
-      <c r="B69" s="19" t="s">
-        <v>788</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="19" t="s">
+      <c r="B84" s="17" t="s">
         <v>603</v>
       </c>
-      <c r="B70" s="19" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="19" t="s">
-        <v>605</v>
-      </c>
-      <c r="B71" s="19" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="19" t="s">
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="17" t="s">
         <v>606</v>
       </c>
-      <c r="B72" s="19" t="s">
+      <c r="B85" s="17" t="s">
         <v>607</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="19" t="s">
-        <v>608</v>
-      </c>
-      <c r="B73" s="19" t="s">
-        <v>609</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="19" t="s">
-        <v>557</v>
-      </c>
-      <c r="B74" s="19" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="19" t="s">
-        <v>610</v>
-      </c>
-      <c r="B75" s="19" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="19" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" s="19" t="s">
-        <v>612</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="19" t="s">
-        <v>10</v>
-      </c>
-      <c r="B77" s="19" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="19" t="s">
-        <v>614</v>
-      </c>
-      <c r="B78" s="19" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="19" t="s">
-        <v>618</v>
-      </c>
-      <c r="B79" s="19" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="19" t="s">
-        <v>622</v>
-      </c>
-      <c r="B80" s="19" t="s">
-        <v>623</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="19" t="s">
-        <v>626</v>
-      </c>
-      <c r="B81" s="19" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="19" t="s">
-        <v>616</v>
-      </c>
-      <c r="B82" s="19" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="19" t="s">
-        <v>620</v>
-      </c>
-      <c r="B83" s="19" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="19" t="s">
-        <v>624</v>
-      </c>
-      <c r="B84" s="19" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="19" t="s">
-        <v>628</v>
-      </c>
-      <c r="B85" s="19" t="s">
-        <v>629</v>
       </c>
     </row>
   </sheetData>

--- a/question_bank/ENGLISH - Grammer.xlsx
+++ b/question_bank/ENGLISH - Grammer.xlsx
@@ -9,20 +9,21 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="2" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="Syllabus" sheetId="26" r:id="rId1"/>
     <sheet name="Convert to Abstarct Noun" sheetId="4" r:id="rId2"/>
     <sheet name="Article" sheetId="20" r:id="rId3"/>
     <sheet name="Preposition" sheetId="19" r:id="rId4"/>
-    <sheet name="Correct Sentences" sheetId="15" r:id="rId5"/>
-    <sheet name="Comparison of Adjectives" sheetId="23" r:id="rId6"/>
-    <sheet name="Formation of Adjectives" sheetId="25" r:id="rId7"/>
+    <sheet name="Conjunction" sheetId="27" r:id="rId5"/>
+    <sheet name="Correct Sentences" sheetId="15" r:id="rId6"/>
+    <sheet name="Comparison of Adjectives" sheetId="23" r:id="rId7"/>
+    <sheet name="Formation of Adjectives" sheetId="25" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Comparison of Adjectives'!$A$1:$B$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Formation of Adjectives'!$A$1:$B$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Comparison of Adjectives'!$A$1:$B$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Formation of Adjectives'!$A$1:$B$85</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -34,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="984">
   <si>
     <t>Anger</t>
   </si>
@@ -5199,13 +5200,565 @@
   </si>
   <si>
     <t>Syllabus</t>
+  </si>
+  <si>
+    <t>*Convert to Abstract Nown</t>
+  </si>
+  <si>
+    <t>*Article</t>
+  </si>
+  <si>
+    <t>*Preposition</t>
+  </si>
+  <si>
+    <t>*Formation of Adjectives</t>
+  </si>
+  <si>
+    <t>ONE CLAUSE JOINED TO ANOTHER CLAUSE</t>
+  </si>
+  <si>
+    <t>KINDS OF CONJUNCTION FOR JOINING CLAUSES</t>
+  </si>
+  <si>
+    <t>Conjunctions are of two types: (1) Co-ordinating (2) Subordinating.</t>
+  </si>
+  <si>
+    <t>My father says ________ this book is mine.</t>
+  </si>
+  <si>
+    <t>My father says {that} this book is mine.</t>
+  </si>
+  <si>
+    <t>He works hard ________ he may succeed.</t>
+  </si>
+  <si>
+    <t>He works hard {that/so that} he may succeed.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I trust his word ________ he speaks the truth. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I trust his word {because} he speaks the truth. </t>
+  </si>
+  <si>
+    <t>The girl will come  ________ she is allowed to do so.</t>
+  </si>
+  <si>
+    <t>The girl will come  {if} she is allowed to do so.</t>
+  </si>
+  <si>
+    <t>I wish to know ________ he will come or not.</t>
+  </si>
+  <si>
+    <t>I wish to know {whether} he will come or not.</t>
+  </si>
+  <si>
+    <t>She walked slowly ________  she should fall down.</t>
+  </si>
+  <si>
+    <t>She walked slowly {lest}  she should fall down.</t>
+  </si>
+  <si>
+    <t>He will do this ________ he is stopped by you.</t>
+  </si>
+  <si>
+    <t>He will do this {unless} he is stopped by you.</t>
+  </si>
+  <si>
+    <t>You may go out ________  the rain has stopped.</t>
+  </si>
+  <si>
+    <t>You may go out {as/since}  the rain has stopped.</t>
+  </si>
+  <si>
+    <t>I wish to know ________ the sick man is today.</t>
+  </si>
+  <si>
+    <t>I wish to know {how} the sick man is today.</t>
+  </si>
+  <si>
+    <t>He left his bed ________ the sun peeped in the room.</t>
+  </si>
+  <si>
+    <t>He left his bed {when} the sun peeped in the room.</t>
+  </si>
+  <si>
+    <t>No one could find out ________ the rogue was lying hid.</t>
+  </si>
+  <si>
+    <t>No one could find out {where} the rogue was lying hid.</t>
+  </si>
+  <si>
+    <t>No one could tell ________  the noise arose.</t>
+  </si>
+  <si>
+    <t>No one could tell {whence}  the noise arose.</t>
+  </si>
+  <si>
+    <t>The mice will play ________ the cat is away.</t>
+  </si>
+  <si>
+    <t>The mice will play {while} the cat is away.</t>
+  </si>
+  <si>
+    <t>You must wait here ________ your father comes back.</t>
+  </si>
+  <si>
+    <t>You must wait here {till/until} your father comes back.</t>
+  </si>
+  <si>
+    <t>They could not tell ________ they were fined.</t>
+  </si>
+  <si>
+    <t>They could not tell {why} they were fined.</t>
+  </si>
+  <si>
+    <t>The girl is quick ________ (she) reads very well.</t>
+  </si>
+  <si>
+    <t>The girl is quick {and} (she) reads very well.</t>
+  </si>
+  <si>
+    <t>The girl is clever ________ (she) cannot do the work.</t>
+  </si>
+  <si>
+    <t>The girl is clever {but} (she) cannot do the work.</t>
+  </si>
+  <si>
+    <t>She went to bed ________ she felt very tired.</t>
+  </si>
+  <si>
+    <t>She went to bed {for/as} she felt very tired.</t>
+  </si>
+  <si>
+    <t>He closed the door ________ his friends had gone.</t>
+  </si>
+  <si>
+    <t>He closed the door {after } his friends had gone.</t>
+  </si>
+  <si>
+    <t>He had his house cleaned ________ his friends came.</t>
+  </si>
+  <si>
+    <t>He had his house cleaned {before} his friends came.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I will trust you ________ you sign your name. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">I will trust you {provided} you sign your name. </t>
+  </si>
+  <si>
+    <t>He will not escape death  ________  rich he may be.</t>
+  </si>
+  <si>
+    <t>He will not escape death  {however}  rich he may be.</t>
+  </si>
+  <si>
+    <t>He left the house ________ the rain stopped.</t>
+  </si>
+  <si>
+    <t>He left the house {as soon as} the rain stopped.</t>
+  </si>
+  <si>
+    <t>He could not pass ________ he tried often.</t>
+  </si>
+  <si>
+    <t>He could not pass {though} he tried often.</t>
+  </si>
+  <si>
+    <t>Your uncle is older ________ your aunt (is).</t>
+  </si>
+  <si>
+    <t>Your uncle is older {than} your aunt (is).</t>
+  </si>
+  <si>
+    <t>It is a long time ________ I saw you last.</t>
+  </si>
+  <si>
+    <t>It is a long time {since} I saw you last.</t>
+  </si>
+  <si>
+    <t>Fill in the blanks with proper Conjunction</t>
+  </si>
+  <si>
+    <t>He is ________ a fool _________ a knave.</t>
+  </si>
+  <si>
+    <t>Did you ever seen _________ a place __________ this?</t>
+  </si>
+  <si>
+    <t>He is _________ wise _________ good.</t>
+  </si>
+  <si>
+    <t>He is _________ wise _________ also good.</t>
+  </si>
+  <si>
+    <t>He must _________ work _________ go.</t>
+  </si>
+  <si>
+    <t>He behaved _________ wisely _________ kindly.</t>
+  </si>
+  <si>
+    <t>He is _________ weak _________ he cannot walk.</t>
+  </si>
+  <si>
+    <t>_________ was her beauty _________ everybody loved her.</t>
+  </si>
+  <si>
+    <t>_________ had I sat down _________ they left the room.</t>
+  </si>
+  <si>
+    <t>_________ had I left the room _________ it began to rain.</t>
+  </si>
+  <si>
+    <t>She has none _________    _________ her mother.</t>
+  </si>
+  <si>
+    <t>She has none _________   _________ her mother.</t>
+  </si>
+  <si>
+    <t>There are some conjunctions that go in pairs. They are called Correlatives. They are both-and; either-or, neither-nor, not only-but also; so-that; such- as; such-that; no sooner than; hardly-when; scarcely-when; else—than; else--but.</t>
+  </si>
+  <si>
+    <t>Subordinating Conjunctions denote time, place, cause, effect, purpose, manner, condition, comparison, apposition (e.g. He wrote to us {that} he would come) and concession (e.g. {However} strong you may be, you cannot do this.)</t>
+  </si>
+  <si>
+    <t>Co-ordinating Conj.</t>
+  </si>
+  <si>
+    <t>Subordinating Conj.</t>
+  </si>
+  <si>
+    <t>Co-ordinating Conjunctions are of four types: (a) Cumulative - and, both... and, as well as etc. (b) Alternative - or, either.....or, neither.....nor etc. (c) Adversative - but, yet, still etc. (d) Illative - so, therefore, etc.</t>
+  </si>
+  <si>
+    <t>He played well _________ got a prize.</t>
+  </si>
+  <si>
+    <t>_________ he _________ his brother will go.</t>
+  </si>
+  <si>
+    <t>Read _________ you will fail.</t>
+  </si>
+  <si>
+    <t>She is sad _________ hopeful.</t>
+  </si>
+  <si>
+    <t>Dipu _________ his brother is honest.</t>
+  </si>
+  <si>
+    <t>He said _________ he would go.</t>
+  </si>
+  <si>
+    <t>Shut the door _________ the child may not go out.</t>
+  </si>
+  <si>
+    <t>He worked hard _________ he might pass the exam.</t>
+  </si>
+  <si>
+    <t>I'll go _________ you come.</t>
+  </si>
+  <si>
+    <t>_________ he is poor, he is honest.</t>
+  </si>
+  <si>
+    <t>_________ it was hard, he did it.</t>
+  </si>
+  <si>
+    <t>He played well {and} got a prize.</t>
+  </si>
+  <si>
+    <t>{Both} he {and} his brother will go.</t>
+  </si>
+  <si>
+    <t>Read {or} you will fail.</t>
+  </si>
+  <si>
+    <t>She is sad {but} hopeful.</t>
+  </si>
+  <si>
+    <t>Dipu {as well as} his brother is honest.</t>
+  </si>
+  <si>
+    <t>He said {that} he would go.</t>
+  </si>
+  <si>
+    <t>Shut the door {so that} the child may not go out.</t>
+  </si>
+  <si>
+    <t>He worked hard {in order that} he might pass the exam.</t>
+  </si>
+  <si>
+    <t>I'll go {if} you come.</t>
+  </si>
+  <si>
+    <t>{Though} he is poor, he is honest.</t>
+  </si>
+  <si>
+    <t>{Although} it was hard, he did it.</t>
+  </si>
+  <si>
+    <t>He worked hard, __________ he failed.</t>
+  </si>
+  <si>
+    <t>Try hard, __________ you will fail.</t>
+  </si>
+  <si>
+    <t>He tried hard, __________ he could win the game.</t>
+  </si>
+  <si>
+    <t>Life is full of tears __________ none wishes to die.</t>
+  </si>
+  <si>
+    <t>You failed __________ your brother passed.</t>
+  </si>
+  <si>
+    <t>He is rich __________ his brother is poor.</t>
+  </si>
+  <si>
+    <t>__________ he __________ his brother __________ will go there.</t>
+  </si>
+  <si>
+    <t>Peter plays __________ the drum, __________ the flute.</t>
+  </si>
+  <si>
+    <t>She will __________ do this __________ leave the room.</t>
+  </si>
+  <si>
+    <t>Do __________ you like.</t>
+  </si>
+  <si>
+    <t>__________ I am ill, I cannot go.</t>
+  </si>
+  <si>
+    <t>Poor __________ I am, I am honest.</t>
+  </si>
+  <si>
+    <t>He cannot go out __________ he is ill.</t>
+  </si>
+  <si>
+    <t>He came __________ I was there.</t>
+  </si>
+  <si>
+    <t>You may go __________ you like.</t>
+  </si>
+  <si>
+    <t>__________ I am ill, I cannot go out.</t>
+  </si>
+  <si>
+    <t>The patient had died __________ the doctor came.</t>
+  </si>
+  <si>
+    <t>He came __________ I had left the place.</t>
+  </si>
+  <si>
+    <t>Make haste __________ the sun shines.</t>
+  </si>
+  <si>
+    <t>Wait __________ the train stops.</t>
+  </si>
+  <si>
+    <t>Do not detrain __________ the train stops.</t>
+  </si>
+  <si>
+    <t>I shall fail __________ you help me.</t>
+  </si>
+  <si>
+    <t>I asked him __________ he would go there.</t>
+  </si>
+  <si>
+    <t>Work hard __________ you should fail.</t>
+  </si>
+  <si>
+    <t>He worked hard, {still} he failed.</t>
+  </si>
+  <si>
+    <t>Try hard, {otherwise} you will fail.</t>
+  </si>
+  <si>
+    <t>He tried hard, {so} he could win the game.</t>
+  </si>
+  <si>
+    <t>Life is full of tears {yet} none wishes to die.</t>
+  </si>
+  <si>
+    <t>You failed {while} your brother passed.</t>
+  </si>
+  <si>
+    <t>He is rich {whereas} his brother is poor.</t>
+  </si>
+  <si>
+    <t>{Not only} he {but} his brother {also} will go there.</t>
+  </si>
+  <si>
+    <t>Peter plays {not only} the drum, {but} also the flute.</t>
+  </si>
+  <si>
+    <t>{Either} do {or} leave it.</t>
+  </si>
+  <si>
+    <t>__________ do __________ leave it.</t>
+  </si>
+  <si>
+    <t>She will {neither} do this {nor} leave the room.</t>
+  </si>
+  <si>
+    <t>Do {as} you like.</t>
+  </si>
+  <si>
+    <t>{As} I am ill, I cannot go.</t>
+  </si>
+  <si>
+    <t>Poor {as (= though)} I am, I am honest.</t>
+  </si>
+  <si>
+    <t>He cannot go out {because} he is ill.</t>
+  </si>
+  <si>
+    <t>He came {when} I was there.</t>
+  </si>
+  <si>
+    <t>You may go {where} you like.</t>
+  </si>
+  <si>
+    <t>{Since} I am ill, I cannot go out.</t>
+  </si>
+  <si>
+    <t>The patient had died {before} the doctor came.</t>
+  </si>
+  <si>
+    <t>He came {after} I had left the place.</t>
+  </si>
+  <si>
+    <t>Make haste {while} the sun shines.</t>
+  </si>
+  <si>
+    <t>Wait {till} the train stops.</t>
+  </si>
+  <si>
+    <t>Do not detrain {until} the train stops.</t>
+  </si>
+  <si>
+    <t>I shall fail {unless} you help me.</t>
+  </si>
+  <si>
+    <t>I asked him {whether/if} he would go there.</t>
+  </si>
+  <si>
+    <t>Work hard {lest} you should fail.</t>
+  </si>
+  <si>
+    <t>You must get up __________ the sun rises.</t>
+  </si>
+  <si>
+    <t>You need not leave your bed __________ the sun rises.</t>
+  </si>
+  <si>
+    <t>I could not find out _________ he lived.</t>
+  </si>
+  <si>
+    <t>Wait here __________ I return.</t>
+  </si>
+  <si>
+    <t>Take care _________ you should fall.</t>
+  </si>
+  <si>
+    <t>You are much more idle _________ you used to be.</t>
+  </si>
+  <si>
+    <t>Many years have passed __________ I saw you last.</t>
+  </si>
+  <si>
+    <t>I wish to know _________ you have been so lazy as before.</t>
+  </si>
+  <si>
+    <t>Tell me _________ you can do it __________ the clock will strike nine.</t>
+  </si>
+  <si>
+    <t>A man must do his best __________ he may succeed.</t>
+  </si>
+  <si>
+    <t>You should not despair __________ you have failed once.</t>
+  </si>
+  <si>
+    <t>Gora sells both apples ___________ oranges.</t>
+  </si>
+  <si>
+    <t>Most insects have wings __________ most ants do not have.</t>
+  </si>
+  <si>
+    <t>Who sweeps the rooms, washes the clothes __________ cooks the meals?</t>
+  </si>
+  <si>
+    <t>Gahar is hard working __________ he is not an intelligent boy.</t>
+  </si>
+  <si>
+    <t>Hashina is thin __________ tall, __________ her brother is fat __________ short.</t>
+  </si>
+  <si>
+    <t>Will you meet me at 4 pm. ___________ 4.30 pm.?</t>
+  </si>
+  <si>
+    <t>The girls are helping their mother __________ the boys are flying kites.</t>
+  </si>
+  <si>
+    <t>__________ you keep on your habit, you may land up in jail.</t>
+  </si>
+  <si>
+    <t>EXERCISE</t>
+  </si>
+  <si>
+    <t>x</t>
+  </si>
+  <si>
+    <t>*Conjunction</t>
+  </si>
+  <si>
+    <t>Noun to Noun - He is {both} a fool {and} a knave.</t>
+  </si>
+  <si>
+    <t>Noun to Pronoun - Did you ever seen {such} a place {as} this?</t>
+  </si>
+  <si>
+    <t>Adjective to Adjective - He is {both} wise {and} good.</t>
+  </si>
+  <si>
+    <t>Adjective to Adjective - He is {not only} wise {but} also good.</t>
+  </si>
+  <si>
+    <t>Verb to Verb - He must {either} work {or} go.</t>
+  </si>
+  <si>
+    <t>Adverb to Adverb - He behaved {neither} wisely {nor} kindly.</t>
+  </si>
+  <si>
+    <t>Adv. and Clause - He is {so} weak {that} he cannot walk.</t>
+  </si>
+  <si>
+    <t>Adv. and Clause - {Such} was her beauty {that} everybody loved her.</t>
+  </si>
+  <si>
+    <t>Adv. and Clause - {No sooner} had I sat down {than} they left the room.</t>
+  </si>
+  <si>
+    <t>Adv. and Clause - {Hardly} had I left the room {when} it began to rain.</t>
+  </si>
+  <si>
+    <t>Adv. and Clause - {Scarcely} had I left the room {when} it began to rain.</t>
+  </si>
+  <si>
+    <t>Adv. and Clause - She has none {else} {than} her mother.</t>
+  </si>
+  <si>
+    <t>Adv. and Clause - She has none {else} {but} her mother.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -5288,8 +5841,17 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -5299,6 +5861,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -5340,7 +5908,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5393,6 +5961,34 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -5675,7 +6271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="139.140625" bestFit="1" customWidth="1"/>
@@ -5738,166 +6334,199 @@
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>772</v>
-      </c>
-      <c r="B8">
-        <v>8</v>
+      <c r="A8" s="25" t="s">
+        <v>800</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>773</v>
+      </c>
+      <c r="B10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="25" t="s">
         <v>774</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>775</v>
-      </c>
-      <c r="B11">
-        <v>11</v>
-      </c>
-    </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>776</v>
-      </c>
-      <c r="B12">
-        <v>12</v>
+      <c r="A12" s="25" t="s">
+        <v>803</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="B13">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="B14">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="B15">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>780</v>
-      </c>
-      <c r="B16">
-        <v>16</v>
+      <c r="A16" s="25" t="s">
+        <v>801</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>781</v>
-      </c>
-      <c r="B17">
-        <v>17</v>
+      <c r="A17" s="25" t="s">
+        <v>802</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>782</v>
-      </c>
-      <c r="B18">
-        <v>18</v>
+      <c r="A18" s="25" t="s">
+        <v>970</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>783</v>
+      <c r="A19" t="s">
+        <v>778</v>
       </c>
       <c r="B19">
-        <v>19</v>
+        <v>14</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>784</v>
+        <v>779</v>
       </c>
       <c r="B20">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>785</v>
+        <v>780</v>
       </c>
       <c r="B21">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>786</v>
+        <v>781</v>
       </c>
       <c r="B22">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>787</v>
+        <v>782</v>
       </c>
       <c r="B23">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>788</v>
+      <c r="A24" s="17" t="s">
+        <v>783</v>
       </c>
       <c r="B24">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>789</v>
+        <v>784</v>
       </c>
       <c r="B25">
-        <v>25</v>
+        <v>20</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>790</v>
+        <v>785</v>
       </c>
       <c r="B26">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
+        <v>786</v>
+      </c>
+      <c r="B27">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>787</v>
+      </c>
+      <c r="B28">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>788</v>
+      </c>
+      <c r="B29">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>789</v>
+      </c>
+      <c r="B30">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>790</v>
+      </c>
+      <c r="B31">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
         <v>791</v>
       </c>
-      <c r="B27">
+      <c r="B32">
         <v>27</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A8" location="'Convert to Abstarct Noun'!A1" display="*Convert to Abstract Nown"/>
+    <hyperlink ref="A16" location="Article!A1" display="*Article"/>
+    <hyperlink ref="A17" location="Preposition!A1" display="*Preposition"/>
+    <hyperlink ref="A11" location="'Comparison of Adjectives'!A1" display="9.  Degrees Of Comparison Of Adjectives"/>
+    <hyperlink ref="A12" location="'Formation of Adjectives'!A1" display="*Formation of Adjectives"/>
+    <hyperlink ref="A18" location="Conjunction!A1" display="*Conjunction"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -7361,6 +7990,850 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C104"/>
+  <sheetFormatPr defaultColWidth="62.85546875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="69.85546875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="65.28515625" style="26" customWidth="1"/>
+    <col min="3" max="16384" width="62.85546875" style="26"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="27" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="34" t="s">
+        <v>859</v>
+      </c>
+      <c r="B1" s="27" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>860</v>
+      </c>
+      <c r="B3" s="26" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>861</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>862</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>863</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>864</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>865</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>866</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
+        <v>867</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>868</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>869</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>869</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>870</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>871</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="30" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>807</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
+        <v>809</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
+        <v>811</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="26" t="s">
+        <v>813</v>
+      </c>
+      <c r="B20" s="26" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>815</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>816</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
+        <v>817</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
+        <v>819</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="28" t="s">
+        <v>821</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="28" t="s">
+        <v>823</v>
+      </c>
+      <c r="B25" s="28" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="28" t="s">
+        <v>825</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="28" t="s">
+        <v>827</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>828</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="28" t="s">
+        <v>829</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="28" t="s">
+        <v>831</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="28" t="s">
+        <v>833</v>
+      </c>
+      <c r="B30" s="28" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="28" t="s">
+        <v>835</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="28" t="s">
+        <v>837</v>
+      </c>
+      <c r="B32" s="28" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="28" t="s">
+        <v>839</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="28" t="s">
+        <v>841</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="28" t="s">
+        <v>843</v>
+      </c>
+      <c r="B35" s="28" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="28" t="s">
+        <v>845</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="28" t="s">
+        <v>847</v>
+      </c>
+      <c r="B37" s="28" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="28" t="s">
+        <v>849</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="28" t="s">
+        <v>851</v>
+      </c>
+      <c r="B39" s="28" t="s">
+        <v>852</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="28" t="s">
+        <v>853</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>854</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="28" t="s">
+        <v>855</v>
+      </c>
+      <c r="B41" s="28" t="s">
+        <v>856</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="28" t="s">
+        <v>857</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="30" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="30" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+      <c r="A45" s="33" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+      <c r="A46" s="33" t="s">
+        <v>873</v>
+      </c>
+      <c r="C46" s="28"/>
+    </row>
+    <row r="47" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="29" t="s">
+        <v>874</v>
+      </c>
+      <c r="C47" s="28"/>
+    </row>
+    <row r="48" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="26" t="s">
+        <v>877</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>888</v>
+      </c>
+      <c r="C48" s="28"/>
+    </row>
+    <row r="49" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="26" t="s">
+        <v>878</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>889</v>
+      </c>
+      <c r="C49" s="28"/>
+    </row>
+    <row r="50" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="26" t="s">
+        <v>879</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>890</v>
+      </c>
+      <c r="C50" s="28"/>
+    </row>
+    <row r="51" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
+        <v>880</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>891</v>
+      </c>
+      <c r="C51" s="28"/>
+    </row>
+    <row r="52" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="26" t="s">
+        <v>881</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>892</v>
+      </c>
+      <c r="C52" s="28"/>
+    </row>
+    <row r="53" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="26" t="s">
+        <v>899</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>923</v>
+      </c>
+      <c r="C53" s="28"/>
+    </row>
+    <row r="54" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="26" t="s">
+        <v>900</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>924</v>
+      </c>
+      <c r="C54" s="28"/>
+    </row>
+    <row r="55" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="26" t="s">
+        <v>901</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>925</v>
+      </c>
+      <c r="C55" s="28"/>
+    </row>
+    <row r="56" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="26" t="s">
+        <v>902</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>926</v>
+      </c>
+      <c r="C56" s="28"/>
+    </row>
+    <row r="57" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>903</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>927</v>
+      </c>
+      <c r="C57" s="28"/>
+    </row>
+    <row r="58" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="26" t="s">
+        <v>904</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>928</v>
+      </c>
+      <c r="C58" s="28"/>
+    </row>
+    <row r="59" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="26" t="s">
+        <v>905</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>929</v>
+      </c>
+      <c r="C59" s="28"/>
+    </row>
+    <row r="60" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="26" t="s">
+        <v>906</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>930</v>
+      </c>
+      <c r="C60" s="28"/>
+    </row>
+    <row r="61" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="26" t="s">
+        <v>932</v>
+      </c>
+      <c r="B61" s="26" t="s">
+        <v>931</v>
+      </c>
+      <c r="C61" s="28"/>
+    </row>
+    <row r="62" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="26" t="s">
+        <v>907</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>933</v>
+      </c>
+      <c r="C62" s="28"/>
+    </row>
+    <row r="63" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="29" t="s">
+        <v>875</v>
+      </c>
+      <c r="C63" s="28"/>
+    </row>
+    <row r="64" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="26" t="s">
+        <v>882</v>
+      </c>
+      <c r="B64" s="26" t="s">
+        <v>893</v>
+      </c>
+      <c r="C64" s="28"/>
+    </row>
+    <row r="65" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="26" t="s">
+        <v>883</v>
+      </c>
+      <c r="B65" s="26" t="s">
+        <v>894</v>
+      </c>
+      <c r="C65" s="28"/>
+    </row>
+    <row r="66" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="26" t="s">
+        <v>884</v>
+      </c>
+      <c r="B66" s="26" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="26" t="s">
+        <v>885</v>
+      </c>
+      <c r="B67" s="26" t="s">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="26" t="s">
+        <v>886</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>897</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>887</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="26" t="s">
+        <v>908</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="26" t="s">
+        <v>909</v>
+      </c>
+      <c r="B71" s="26" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="26" t="s">
+        <v>910</v>
+      </c>
+      <c r="B72" s="26" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="26" t="s">
+        <v>911</v>
+      </c>
+      <c r="B73" s="26" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="26" t="s">
+        <v>912</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="26" t="s">
+        <v>913</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="26" t="s">
+        <v>914</v>
+      </c>
+      <c r="B76" s="26" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="26" t="s">
+        <v>915</v>
+      </c>
+      <c r="B77" s="26" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="26" t="s">
+        <v>916</v>
+      </c>
+      <c r="B78" s="26" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="26" t="s">
+        <v>917</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="26" t="s">
+        <v>918</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="26" t="s">
+        <v>919</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="26" t="s">
+        <v>920</v>
+      </c>
+      <c r="B82" s="26" t="s">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="26" t="s">
+        <v>921</v>
+      </c>
+      <c r="B83" s="26" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="26" t="s">
+        <v>922</v>
+      </c>
+      <c r="B84" s="26" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="31" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="26" t="s">
+        <v>949</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="26" t="s">
+        <v>950</v>
+      </c>
+      <c r="B87" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="26" t="s">
+        <v>951</v>
+      </c>
+      <c r="B88" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="26" t="s">
+        <v>952</v>
+      </c>
+      <c r="B89" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="26" t="s">
+        <v>953</v>
+      </c>
+      <c r="B90" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="26" t="s">
+        <v>954</v>
+      </c>
+      <c r="B91" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="26" t="s">
+        <v>955</v>
+      </c>
+      <c r="B92" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="26" t="s">
+        <v>956</v>
+      </c>
+      <c r="B93" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="26" t="s">
+        <v>957</v>
+      </c>
+      <c r="B94" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="26" t="s">
+        <v>958</v>
+      </c>
+      <c r="B95" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="26" t="s">
+        <v>959</v>
+      </c>
+      <c r="B96" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="26" t="s">
+        <v>960</v>
+      </c>
+      <c r="B97" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="26" t="s">
+        <v>961</v>
+      </c>
+      <c r="B98" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="26" t="s">
+        <v>962</v>
+      </c>
+      <c r="B99" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="26" t="s">
+        <v>963</v>
+      </c>
+      <c r="B100" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="26" t="s">
+        <v>964</v>
+      </c>
+      <c r="B101" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="26" t="s">
+        <v>965</v>
+      </c>
+      <c r="B102" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="103" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="26" t="s">
+        <v>966</v>
+      </c>
+      <c r="B103" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="104" spans="1:2" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="26" t="s">
+        <v>967</v>
+      </c>
+      <c r="B104" s="26" t="s">
+        <v>969</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Syllabus!A1" display="Fill in the blanks with proper Conjunction"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7608,7 +9081,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>94</v>
       </c>
@@ -7896,7 +9369,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8475,7 +9948,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/question_bank/ENGLISH - Grammer.xlsx
+++ b/question_bank/ENGLISH - Grammer.xlsx
@@ -9,21 +9,22 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="4"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Syllabus" sheetId="26" r:id="rId1"/>
-    <sheet name="Convert to Abstarct Noun" sheetId="4" r:id="rId2"/>
-    <sheet name="Article" sheetId="20" r:id="rId3"/>
-    <sheet name="Preposition" sheetId="19" r:id="rId4"/>
-    <sheet name="Conjunction" sheetId="27" r:id="rId5"/>
-    <sheet name="Correct Sentences" sheetId="15" r:id="rId6"/>
-    <sheet name="Comparison of Adjectives" sheetId="23" r:id="rId7"/>
-    <sheet name="Formation of Adjectives" sheetId="25" r:id="rId8"/>
+    <sheet name="Gendor" sheetId="28" r:id="rId2"/>
+    <sheet name="Convert to Abstarct Noun" sheetId="4" r:id="rId3"/>
+    <sheet name="Article" sheetId="20" r:id="rId4"/>
+    <sheet name="Preposition" sheetId="19" r:id="rId5"/>
+    <sheet name="Conjunction" sheetId="27" r:id="rId6"/>
+    <sheet name="Correct Sentences" sheetId="15" r:id="rId7"/>
+    <sheet name="Comparison of Adjectives" sheetId="23" r:id="rId8"/>
+    <sheet name="Formation of Adjectives" sheetId="25" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Comparison of Adjectives'!$A$1:$B$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Formation of Adjectives'!$A$1:$B$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Comparison of Adjectives'!$A$1:$B$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Formation of Adjectives'!$A$1:$B$85</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1011" uniqueCount="984">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="1149">
   <si>
     <t>Anger</t>
   </si>
@@ -5752,6 +5753,501 @@
   </si>
   <si>
     <t>Adv. and Clause - She has none {else} {but} her mother.</t>
+  </si>
+  <si>
+    <t>Masculine -- Feminine</t>
+  </si>
+  <si>
+    <t>Patron</t>
+  </si>
+  <si>
+    <t>patroness</t>
+  </si>
+  <si>
+    <t>Note that in the following -ess is added after dropping the vowel of the masculine ending</t>
+  </si>
+  <si>
+    <t>By placing a word before or after</t>
+  </si>
+  <si>
+    <t>Bachelor</t>
+  </si>
+  <si>
+    <t>maid, spinster</t>
+  </si>
+  <si>
+    <t>girl</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>sister</t>
+  </si>
+  <si>
+    <t>Buck</t>
+  </si>
+  <si>
+    <t>doe</t>
+  </si>
+  <si>
+    <t>Bull (or ox)</t>
+  </si>
+  <si>
+    <t>cow</t>
+  </si>
+  <si>
+    <t>Bullock</t>
+  </si>
+  <si>
+    <t>heifer</t>
+  </si>
+  <si>
+    <t>Cock</t>
+  </si>
+  <si>
+    <t>hen</t>
+  </si>
+  <si>
+    <t>Colt</t>
+  </si>
+  <si>
+    <t>filly</t>
+  </si>
+  <si>
+    <t>Dog</t>
+  </si>
+  <si>
+    <t>bitch</t>
+  </si>
+  <si>
+    <t>Drake</t>
+  </si>
+  <si>
+    <t>duck</t>
+  </si>
+  <si>
+    <t>Drone</t>
+  </si>
+  <si>
+    <t>bee</t>
+  </si>
+  <si>
+    <t>Earl</t>
+  </si>
+  <si>
+    <t>countess</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>Gander</t>
+  </si>
+  <si>
+    <t>goose</t>
+  </si>
+  <si>
+    <t>Gentleman</t>
+  </si>
+  <si>
+    <t>lady</t>
+  </si>
+  <si>
+    <t>Hart</t>
+  </si>
+  <si>
+    <t>roe</t>
+  </si>
+  <si>
+    <t>Horse</t>
+  </si>
+  <si>
+    <t>mare</t>
+  </si>
+  <si>
+    <t>Husband</t>
+  </si>
+  <si>
+    <t>wife</t>
+  </si>
+  <si>
+    <t>queen</t>
+  </si>
+  <si>
+    <t>Lord</t>
+  </si>
+  <si>
+    <t>Monk (or friar)</t>
+  </si>
+  <si>
+    <t>nun</t>
+  </si>
+  <si>
+    <t>Nephew</t>
+  </si>
+  <si>
+    <t>niece</t>
+  </si>
+  <si>
+    <t>Papa</t>
+  </si>
+  <si>
+    <t>mamma</t>
+  </si>
+  <si>
+    <t>Ram</t>
+  </si>
+  <si>
+    <t>ewe</t>
+  </si>
+  <si>
+    <t>Sir</t>
+  </si>
+  <si>
+    <t>madam</t>
+  </si>
+  <si>
+    <t>Son</t>
+  </si>
+  <si>
+    <t>daughter</t>
+  </si>
+  <si>
+    <t>Stag</t>
+  </si>
+  <si>
+    <t>hind</t>
+  </si>
+  <si>
+    <t>Uncle</t>
+  </si>
+  <si>
+    <t>aunt</t>
+  </si>
+  <si>
+    <t>Wizard</t>
+  </si>
+  <si>
+    <t>witch</t>
+  </si>
+  <si>
+    <t>Author</t>
+  </si>
+  <si>
+    <t>authoress</t>
+  </si>
+  <si>
+    <t>Baron</t>
+  </si>
+  <si>
+    <t>baroness</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Giant</t>
+  </si>
+  <si>
+    <t>giantess</t>
+  </si>
+  <si>
+    <t>Heir</t>
+  </si>
+  <si>
+    <t>heiress</t>
+  </si>
+  <si>
+    <t>Host</t>
+  </si>
+  <si>
+    <t>hostess</t>
+  </si>
+  <si>
+    <t>Jew</t>
+  </si>
+  <si>
+    <t>Jewess</t>
+  </si>
+  <si>
+    <t>Lion</t>
+  </si>
+  <si>
+    <t>lioness</t>
+  </si>
+  <si>
+    <t>Manager</t>
+  </si>
+  <si>
+    <t>manageress</t>
+  </si>
+  <si>
+    <t>Mayor</t>
+  </si>
+  <si>
+    <t>mayoress</t>
+  </si>
+  <si>
+    <t>Peer</t>
+  </si>
+  <si>
+    <t>peeress</t>
+  </si>
+  <si>
+    <t>Poet</t>
+  </si>
+  <si>
+    <t>poetess</t>
+  </si>
+  <si>
+    <t>Priest</t>
+  </si>
+  <si>
+    <t>priestess</t>
+  </si>
+  <si>
+    <t>Prophet</t>
+  </si>
+  <si>
+    <t>prophetess</t>
+  </si>
+  <si>
+    <t>Shepherd</t>
+  </si>
+  <si>
+    <t>shepherdess</t>
+  </si>
+  <si>
+    <t>Steward</t>
+  </si>
+  <si>
+    <t>stewardess</t>
+  </si>
+  <si>
+    <t>Viscount</t>
+  </si>
+  <si>
+    <t>viscountess</t>
+  </si>
+  <si>
+    <t>Actor</t>
+  </si>
+  <si>
+    <t>actress</t>
+  </si>
+  <si>
+    <t>Benefactor</t>
+  </si>
+  <si>
+    <t>benefactress</t>
+  </si>
+  <si>
+    <t>Conductor</t>
+  </si>
+  <si>
+    <t>conductress</t>
+  </si>
+  <si>
+    <t>Enchanter</t>
+  </si>
+  <si>
+    <t>enchantress</t>
+  </si>
+  <si>
+    <t>Founder</t>
+  </si>
+  <si>
+    <t>foundress</t>
+  </si>
+  <si>
+    <t>Hunter</t>
+  </si>
+  <si>
+    <t>huntress</t>
+  </si>
+  <si>
+    <t>Instructor</t>
+  </si>
+  <si>
+    <t>instructress</t>
+  </si>
+  <si>
+    <t>Negro</t>
+  </si>
+  <si>
+    <t>negress</t>
+  </si>
+  <si>
+    <t>Abbot</t>
+  </si>
+  <si>
+    <t>abbess</t>
+  </si>
+  <si>
+    <t>Duke</t>
+  </si>
+  <si>
+    <t>duchess</t>
+  </si>
+  <si>
+    <t>Emperor</t>
+  </si>
+  <si>
+    <t>empress</t>
+  </si>
+  <si>
+    <t>Preceptor</t>
+  </si>
+  <si>
+    <t>preceptress</t>
+  </si>
+  <si>
+    <t>Prince</t>
+  </si>
+  <si>
+    <t>princess</t>
+  </si>
+  <si>
+    <t>Songster</t>
+  </si>
+  <si>
+    <t>songstress</t>
+  </si>
+  <si>
+    <t>Tempter</t>
+  </si>
+  <si>
+    <t>temptress</t>
+  </si>
+  <si>
+    <t>Seamster</t>
+  </si>
+  <si>
+    <t>seamstress</t>
+  </si>
+  <si>
+    <t>Tiger</t>
+  </si>
+  <si>
+    <t>tigress</t>
+  </si>
+  <si>
+    <t>Traitor</t>
+  </si>
+  <si>
+    <t>traitress</t>
+  </si>
+  <si>
+    <t>Waiter</t>
+  </si>
+  <si>
+    <t>waitress</t>
+  </si>
+  <si>
+    <t>Master</t>
+  </si>
+  <si>
+    <t>mistress</t>
+  </si>
+  <si>
+    <t>Murderer</t>
+  </si>
+  <si>
+    <t>murderess</t>
+  </si>
+  <si>
+    <t>Sorcerer</t>
+  </si>
+  <si>
+    <t>sorceress</t>
+  </si>
+  <si>
+    <t>Hero</t>
+  </si>
+  <si>
+    <t>heroine</t>
+  </si>
+  <si>
+    <t>Testator</t>
+  </si>
+  <si>
+    <t>testatrix</t>
+  </si>
+  <si>
+    <t>Czar</t>
+  </si>
+  <si>
+    <t>czarina</t>
+  </si>
+  <si>
+    <t>Sultan</t>
+  </si>
+  <si>
+    <t>sultana</t>
+  </si>
+  <si>
+    <t>Signor</t>
+  </si>
+  <si>
+    <t>signora</t>
+  </si>
+  <si>
+    <t>Fox</t>
+  </si>
+  <si>
+    <t>vixen</t>
+  </si>
+  <si>
+    <t>Grandfather</t>
+  </si>
+  <si>
+    <t>grandmother</t>
+  </si>
+  <si>
+    <t>Greatuncle</t>
+  </si>
+  <si>
+    <t>greataunt</t>
+  </si>
+  <si>
+    <t>Manservant</t>
+  </si>
+  <si>
+    <t>maidservant</t>
+  </si>
+  <si>
+    <t>Landlord</t>
+  </si>
+  <si>
+    <t>landlady</t>
+  </si>
+  <si>
+    <t>milkman</t>
+  </si>
+  <si>
+    <t>milkwoman</t>
+  </si>
+  <si>
+    <t>peacock</t>
+  </si>
+  <si>
+    <t>peahen</t>
+  </si>
+  <si>
+    <t>salesman</t>
+  </si>
+  <si>
+    <t>saleswoman</t>
+  </si>
+  <si>
+    <t>washerman</t>
+  </si>
+  <si>
+    <t>washerwoman</t>
+  </si>
+  <si>
+    <t>Change Gendor of the following:</t>
   </si>
 </sst>
 </file>
@@ -5908,7 +6404,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -5989,6 +6485,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -6533,6 +7032,711 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B87"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="44.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>989</v>
+      </c>
+      <c r="B2" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>745</v>
+      </c>
+      <c r="B3" t="s">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>992</v>
+      </c>
+      <c r="B4" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>994</v>
+      </c>
+      <c r="B5" t="s">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>996</v>
+      </c>
+      <c r="B6" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>998</v>
+      </c>
+      <c r="B7" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>1010</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B14" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>1015</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
+        <v>1019</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1020</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="26" t="s">
+        <v>533</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
+        <v>764</v>
+      </c>
+      <c r="B22" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="26" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1030</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="26" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="26" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="26" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="26" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="26" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="26" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="26" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="26" t="s">
+        <v>1048</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1049</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="26" t="s">
+        <v>1050</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="26" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="26" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="26" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1059</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="26" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="26" t="s">
+        <v>985</v>
+      </c>
+      <c r="B42" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="26" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="26" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="26" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="26" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1069</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="26" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="26" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1073</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="26" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="29" t="s">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1077</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="26" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1079</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="26" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="26" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="26" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="26" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1087</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1089</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="26" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="26" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1093</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="26" t="s">
+        <v>1094</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1095</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="26" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1097</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="26" t="s">
+        <v>1098</v>
+      </c>
+      <c r="B62" t="s">
+        <v>1099</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="26" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B63" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="26" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B64" t="s">
+        <v>1103</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="26" t="s">
+        <v>1104</v>
+      </c>
+      <c r="B65" t="s">
+        <v>1105</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="26" t="s">
+        <v>1106</v>
+      </c>
+      <c r="B66" t="s">
+        <v>1107</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="26" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B67" t="s">
+        <v>1109</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="26" t="s">
+        <v>1110</v>
+      </c>
+      <c r="B68" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B69" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="26" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B70" t="s">
+        <v>1115</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="26" t="s">
+        <v>1116</v>
+      </c>
+      <c r="B71" t="s">
+        <v>1117</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="26" t="s">
+        <v>1118</v>
+      </c>
+      <c r="B72" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="26" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="26" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B74" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="26" t="s">
+        <v>1124</v>
+      </c>
+      <c r="B75" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="26" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B76" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="26" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B77" t="s">
+        <v>1129</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="26" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B78" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="35" t="s">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="26" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1133</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="26" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B81" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="26" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B82" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="26" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B83" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="26" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="26" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B85" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="26" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B86" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="26" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -7578,7 +8782,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7739,7 +8943,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -7988,7 +9192,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C104"/>
   <sheetFormatPr defaultColWidth="62.85546875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8832,7 +10036,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9081,7 +10285,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="31" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
         <v>94</v>
       </c>
@@ -9369,7 +10573,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9948,7 +11152,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/question_bank/ENGLISH - Grammer.xlsx
+++ b/question_bank/ENGLISH - Grammer.xlsx
@@ -9,22 +9,26 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="Syllabus" sheetId="26" r:id="rId1"/>
-    <sheet name="Gendor" sheetId="28" r:id="rId2"/>
-    <sheet name="Convert to Abstarct Noun" sheetId="4" r:id="rId3"/>
-    <sheet name="Article" sheetId="20" r:id="rId4"/>
-    <sheet name="Preposition" sheetId="19" r:id="rId5"/>
-    <sheet name="Conjunction" sheetId="27" r:id="rId6"/>
-    <sheet name="Correct Sentences" sheetId="15" r:id="rId7"/>
-    <sheet name="Comparison of Adjectives" sheetId="23" r:id="rId8"/>
-    <sheet name="Formation of Adjectives" sheetId="25" r:id="rId9"/>
+    <sheet name="Gender (HSG)" sheetId="28" r:id="rId2"/>
+    <sheet name="Gender (Guide)" sheetId="29" r:id="rId3"/>
+    <sheet name="Number (HSG)" sheetId="30" r:id="rId4"/>
+    <sheet name="Convert to Abstarct Noun" sheetId="4" r:id="rId5"/>
+    <sheet name="Article" sheetId="20" r:id="rId6"/>
+    <sheet name="Preposition" sheetId="19" r:id="rId7"/>
+    <sheet name="Conjunction" sheetId="27" r:id="rId8"/>
+    <sheet name="Correct Sentences" sheetId="15" r:id="rId9"/>
+    <sheet name="Comparison of Adjectives" sheetId="23" r:id="rId10"/>
+    <sheet name="Formation of Adjectives" sheetId="25" r:id="rId11"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Comparison of Adjectives'!$A$1:$B$70</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Formation of Adjectives'!$A$1:$B$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Comparison of Adjectives'!$A$1:$B$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Formation of Adjectives'!$A$1:$B$85</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Gender (Guide)'!$A$1:$B$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Gender (HSG)'!$A$1:$B$93</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1183" uniqueCount="1149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="1450">
   <si>
     <t>Anger</t>
   </si>
@@ -6247,7 +6251,910 @@
     <t>washerwoman</t>
   </si>
   <si>
-    <t>Change Gendor of the following:</t>
+    <t>Change Gender of the following:</t>
+  </si>
+  <si>
+    <t>By using a entirely different Word:</t>
+  </si>
+  <si>
+    <t>By adding a syllable (-ess, -ine, -trix, -a etc.)</t>
+  </si>
+  <si>
+    <t>1) By using a entirely different Word:</t>
+  </si>
+  <si>
+    <t>2) By adding a syllable (-ess, -ine, -trix, -a etc.)</t>
+  </si>
+  <si>
+    <t>3 )By placing a word before or after</t>
+  </si>
+  <si>
+    <t>Gender can be changed in three ways-</t>
+  </si>
+  <si>
+    <t>Spinster</t>
+  </si>
+  <si>
+    <t>Billy goat</t>
+  </si>
+  <si>
+    <t>Nanny goat</t>
+  </si>
+  <si>
+    <t>Boar</t>
+  </si>
+  <si>
+    <t>(Sow) Pig</t>
+  </si>
+  <si>
+    <t>Girl</t>
+  </si>
+  <si>
+    <t>Bridegroom</t>
+  </si>
+  <si>
+    <t>Bride</t>
+  </si>
+  <si>
+    <t>Sister</t>
+  </si>
+  <si>
+    <t>Bull</t>
+  </si>
+  <si>
+    <t>Cow</t>
+  </si>
+  <si>
+    <t>Hen</t>
+  </si>
+  <si>
+    <t>Filly</t>
+  </si>
+  <si>
+    <t>Conductress</t>
+  </si>
+  <si>
+    <t>Bitch.</t>
+  </si>
+  <si>
+    <t>Duck</t>
+  </si>
+  <si>
+    <t>Drones</t>
+  </si>
+  <si>
+    <t>Bee</t>
+  </si>
+  <si>
+    <t>Empress</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>Vixen</t>
+  </si>
+  <si>
+    <t>Garden</t>
+  </si>
+  <si>
+    <t>Goose</t>
+  </si>
+  <si>
+    <t>Hind (Deer)</t>
+  </si>
+  <si>
+    <t>Head master</t>
+  </si>
+  <si>
+    <t>Head mistress</t>
+  </si>
+  <si>
+    <t>Man Servant</t>
+  </si>
+  <si>
+    <t>Maid servant</t>
+  </si>
+  <si>
+    <t>Prophetess</t>
+  </si>
+  <si>
+    <t>Proprietor</t>
+  </si>
+  <si>
+    <t>Proprietress</t>
+  </si>
+  <si>
+    <t>Shepherdess</t>
+  </si>
+  <si>
+    <t>School master</t>
+  </si>
+  <si>
+    <t>School mistress</t>
+  </si>
+  <si>
+    <t>Aunt</t>
+  </si>
+  <si>
+    <t>Widower</t>
+  </si>
+  <si>
+    <t>Widow</t>
+  </si>
+  <si>
+    <t>Heroine</t>
+  </si>
+  <si>
+    <t>Hostess</t>
+  </si>
+  <si>
+    <t>Huntress</t>
+  </si>
+  <si>
+    <t>Wife</t>
+  </si>
+  <si>
+    <t>Instructress</t>
+  </si>
+  <si>
+    <t>Queen</t>
+  </si>
+  <si>
+    <t>Land Lord</t>
+  </si>
+  <si>
+    <t>Land Lady</t>
+  </si>
+  <si>
+    <t>Lioness</t>
+  </si>
+  <si>
+    <t>Lady</t>
+  </si>
+  <si>
+    <t>Manageress</t>
+  </si>
+  <si>
+    <t>Masseur</t>
+  </si>
+  <si>
+    <t>Masseuree</t>
+  </si>
+  <si>
+    <t>Mistress</t>
+  </si>
+  <si>
+    <t>Mayoress</t>
+  </si>
+  <si>
+    <t>Negrees</t>
+  </si>
+  <si>
+    <t>Neice</t>
+  </si>
+  <si>
+    <t>Peacok</t>
+  </si>
+  <si>
+    <t>Peahen</t>
+  </si>
+  <si>
+    <t>Poetess</t>
+  </si>
+  <si>
+    <t>Prietess</t>
+  </si>
+  <si>
+    <t>Princess</t>
+  </si>
+  <si>
+    <t>Ewe (Sheep)</t>
+  </si>
+  <si>
+    <t>Stallion</t>
+  </si>
+  <si>
+    <t>Mare</t>
+  </si>
+  <si>
+    <t>Tigress</t>
+  </si>
+  <si>
+    <t>Waitress</t>
+  </si>
+  <si>
+    <t>Witch</t>
+  </si>
+  <si>
+    <t>How Plurals are Formed</t>
+  </si>
+  <si>
+    <t>31. (i) The Plural of nouns is generally formed by adding -s to the singular; as,</t>
+  </si>
+  <si>
+    <t>(ii) But Nouns ending in -s, -sh, -ch (soft), or -x form the plural by adding -es to the singular</t>
+  </si>
+  <si>
+    <t>(iii) Most Nouns ending in -o also form the plural by adding -es to the singular</t>
+  </si>
+  <si>
+    <t>(iv) A few nouns ending in -o merely add -s</t>
+  </si>
+  <si>
+    <t>The nouns dwarf, hoof, scarf and wharf take either -s or -ves in the plural.</t>
+  </si>
+  <si>
+    <t>dwarfs or dwarves; hoofs or hooves;</t>
+  </si>
+  <si>
+    <t>scarfs or scarves; wharfs or wharves</t>
+  </si>
+  <si>
+    <t>32. A few nouns form their plural by changing the inside vowel of the singlar</t>
+  </si>
+  <si>
+    <t>33. There are a few nouns that form their plural by adding -en to the singular; as,</t>
+  </si>
+  <si>
+    <t>The plural of fish is fish or fishes. The form fishes is less usual.</t>
+  </si>
+  <si>
+    <t>34. Some nouns have the singular and the plural alike; as,</t>
+  </si>
+  <si>
+    <t>Swine</t>
+  </si>
+  <si>
+    <t>Sheep</t>
+  </si>
+  <si>
+    <t>Deer</t>
+  </si>
+  <si>
+    <t>Cod</t>
+  </si>
+  <si>
+    <t>Trout</t>
+  </si>
+  <si>
+    <t>Salmon</t>
+  </si>
+  <si>
+    <t>Aircraft</t>
+  </si>
+  <si>
+    <t>Spacecraft</t>
+  </si>
+  <si>
+    <t>Series</t>
+  </si>
+  <si>
+    <t>Species</t>
+  </si>
+  <si>
+    <t>Pair</t>
+  </si>
+  <si>
+    <t>Dozen</t>
+  </si>
+  <si>
+    <t>Score</t>
+  </si>
+  <si>
+    <t>Gross</t>
+  </si>
+  <si>
+    <t>Hundred</t>
+  </si>
+  <si>
+    <t>Thousand</t>
+  </si>
+  <si>
+    <t>35. Some nouns are used only in the plural.</t>
+  </si>
+  <si>
+    <t>(1) Names of instruments which have two parts forming a kind of pair; as,</t>
+  </si>
+  <si>
+    <t>(3) Certain other nouns; as,</t>
+  </si>
+  <si>
+    <t>36. Some nouns originally singular are now generally used in the plural; as, Alms, riches, eaves.</t>
+  </si>
+  <si>
+    <t>Riches do many things.</t>
+  </si>
+  <si>
+    <t>37. The following nouns look plural but are in fact singular:</t>
+  </si>
+  <si>
+    <t>(1) Names of subjects</t>
+  </si>
+  <si>
+    <t>mathematics, physics, electronics, etc.</t>
+  </si>
+  <si>
+    <t>(2) The word news</t>
+  </si>
+  <si>
+    <t>(3) Names of some common diseases measles, mumps, rickets</t>
+  </si>
+  <si>
+    <t>(4) Names of some games billiards, draughts</t>
+  </si>
+  <si>
+    <t>Mathematics is his favourite study. No news is good news.</t>
+  </si>
+  <si>
+    <t>India won by an innings and three runs. Measles is infectious.</t>
+  </si>
+  <si>
+    <t>Billiards is my favourite game.</t>
+  </si>
+  <si>
+    <t>38. Certain Collective Nouns, though singular in form, are always used as plurals; as,</t>
+  </si>
+  <si>
+    <t>Poultry, cattle, vermin, people, gentry.</t>
+  </si>
+  <si>
+    <t>These poultry are mine.</t>
+  </si>
+  <si>
+    <t>Whose are these cattle?</t>
+  </si>
+  <si>
+    <t>Vermin destroy our property and carry disease.</t>
+  </si>
+  <si>
+    <t>Who are those people (= persons)?</t>
+  </si>
+  <si>
+    <t>There are few gentry in this town.</t>
+  </si>
+  <si>
+    <t>Note:- As a Common Noun 'people' means a 'nation' and is used in both singular and plural; as,</t>
+  </si>
+  <si>
+    <t>The Japanese are a hard-working people.</t>
+  </si>
+  <si>
+    <t>There are many different peoples in Europe.</t>
+  </si>
+  <si>
+    <t>39. A Compound Noun generally forms its plural by adding -s to the principal word; as,</t>
+  </si>
+  <si>
+    <t>Singular Plural</t>
+  </si>
+  <si>
+    <t>Singular - Plural</t>
+  </si>
+  <si>
+    <t>boys</t>
+  </si>
+  <si>
+    <t>Pen</t>
+  </si>
+  <si>
+    <t>pens</t>
+  </si>
+  <si>
+    <t>girls</t>
+  </si>
+  <si>
+    <t>Desk</t>
+  </si>
+  <si>
+    <t>desks</t>
+  </si>
+  <si>
+    <t>Book</t>
+  </si>
+  <si>
+    <t>books</t>
+  </si>
+  <si>
+    <t>cows</t>
+  </si>
+  <si>
+    <t>Class</t>
+  </si>
+  <si>
+    <t>classes</t>
+  </si>
+  <si>
+    <t>Kiss</t>
+  </si>
+  <si>
+    <t>kisses</t>
+  </si>
+  <si>
+    <t>Dish</t>
+  </si>
+  <si>
+    <t>dishes</t>
+  </si>
+  <si>
+    <t>Brush</t>
+  </si>
+  <si>
+    <t>brushes</t>
+  </si>
+  <si>
+    <t>Match</t>
+  </si>
+  <si>
+    <t>matches</t>
+  </si>
+  <si>
+    <t>Watch</t>
+  </si>
+  <si>
+    <t>watches</t>
+  </si>
+  <si>
+    <t>Branch</t>
+  </si>
+  <si>
+    <t>branches</t>
+  </si>
+  <si>
+    <t>Tax</t>
+  </si>
+  <si>
+    <t>taxes</t>
+  </si>
+  <si>
+    <t>Box</t>
+  </si>
+  <si>
+    <t>boxes.</t>
+  </si>
+  <si>
+    <t>Buffalo</t>
+  </si>
+  <si>
+    <t>buffaloes</t>
+  </si>
+  <si>
+    <t>Mango</t>
+  </si>
+  <si>
+    <t>mangoes</t>
+  </si>
+  <si>
+    <t>heroes</t>
+  </si>
+  <si>
+    <t>Potato</t>
+  </si>
+  <si>
+    <t>potatoes</t>
+  </si>
+  <si>
+    <t>Cargo</t>
+  </si>
+  <si>
+    <t>cargoes</t>
+  </si>
+  <si>
+    <t>Echo</t>
+  </si>
+  <si>
+    <t>echoes</t>
+  </si>
+  <si>
+    <t>negroes</t>
+  </si>
+  <si>
+    <t>Volcano</t>
+  </si>
+  <si>
+    <t>volcanoes</t>
+  </si>
+  <si>
+    <t>Dynamo</t>
+  </si>
+  <si>
+    <t>dynamos</t>
+  </si>
+  <si>
+    <t>Solo</t>
+  </si>
+  <si>
+    <t>solos</t>
+  </si>
+  <si>
+    <t>Ratio</t>
+  </si>
+  <si>
+    <t>ratios</t>
+  </si>
+  <si>
+    <t>Canto</t>
+  </si>
+  <si>
+    <t>cantos</t>
+  </si>
+  <si>
+    <t>Memento</t>
+  </si>
+  <si>
+    <t>mementos</t>
+  </si>
+  <si>
+    <t>Quarto</t>
+  </si>
+  <si>
+    <t>quartos</t>
+  </si>
+  <si>
+    <t>Piano</t>
+  </si>
+  <si>
+    <t>pianos</t>
+  </si>
+  <si>
+    <t>Photo</t>
+  </si>
+  <si>
+    <t>photos</t>
+  </si>
+  <si>
+    <t>Stereo</t>
+  </si>
+  <si>
+    <t>stereos</t>
+  </si>
+  <si>
+    <t>Kilo</t>
+  </si>
+  <si>
+    <t>kilos</t>
+  </si>
+  <si>
+    <t>Logo</t>
+  </si>
+  <si>
+    <t>logos</t>
+  </si>
+  <si>
+    <t>Commando</t>
+  </si>
+  <si>
+    <t>commandos</t>
+  </si>
+  <si>
+    <t>(v) Nouns ending in -y, preceded by a consonant, form their plural by changing -y into --i and adding -es</t>
+  </si>
+  <si>
+    <t>(vi) The following nouns ending in -f or -fe form their plural by changing --f or -fe into v and adding -es</t>
+  </si>
+  <si>
+    <t>Other words ending in --f or -fe add -s</t>
+  </si>
+  <si>
+    <t>Baby</t>
+  </si>
+  <si>
+    <t>babies</t>
+  </si>
+  <si>
+    <t>ladies</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>cities</t>
+  </si>
+  <si>
+    <t>Army</t>
+  </si>
+  <si>
+    <t>armies</t>
+  </si>
+  <si>
+    <t>Story</t>
+  </si>
+  <si>
+    <t>stories</t>
+  </si>
+  <si>
+    <t>Pony</t>
+  </si>
+  <si>
+    <t>ponies</t>
+  </si>
+  <si>
+    <t>Thief</t>
+  </si>
+  <si>
+    <t>thieves</t>
+  </si>
+  <si>
+    <t>wives</t>
+  </si>
+  <si>
+    <t>Wolf</t>
+  </si>
+  <si>
+    <t>wolves</t>
+  </si>
+  <si>
+    <t>lives</t>
+  </si>
+  <si>
+    <t>Calf</t>
+  </si>
+  <si>
+    <t>calves</t>
+  </si>
+  <si>
+    <t>leaf</t>
+  </si>
+  <si>
+    <t>leaves</t>
+  </si>
+  <si>
+    <t>loaf</t>
+  </si>
+  <si>
+    <t>loaves</t>
+  </si>
+  <si>
+    <t>knife</t>
+  </si>
+  <si>
+    <t>knives</t>
+  </si>
+  <si>
+    <t>shelf</t>
+  </si>
+  <si>
+    <t>shelves</t>
+  </si>
+  <si>
+    <t>half</t>
+  </si>
+  <si>
+    <t>halves</t>
+  </si>
+  <si>
+    <t>elf</t>
+  </si>
+  <si>
+    <t>elves</t>
+  </si>
+  <si>
+    <t>self</t>
+  </si>
+  <si>
+    <t>selves</t>
+  </si>
+  <si>
+    <t>sheaf</t>
+  </si>
+  <si>
+    <t>sheaves</t>
+  </si>
+  <si>
+    <t>Chief</t>
+  </si>
+  <si>
+    <t>chiefs</t>
+  </si>
+  <si>
+    <t>Safe</t>
+  </si>
+  <si>
+    <t>safes</t>
+  </si>
+  <si>
+    <t>proof</t>
+  </si>
+  <si>
+    <t>proofs</t>
+  </si>
+  <si>
+    <t>gulf</t>
+  </si>
+  <si>
+    <t>gulfs</t>
+  </si>
+  <si>
+    <t>cliff</t>
+  </si>
+  <si>
+    <t>cliffs</t>
+  </si>
+  <si>
+    <t>handkerchief</t>
+  </si>
+  <si>
+    <t>handkerchiefs</t>
+  </si>
+  <si>
+    <t>men</t>
+  </si>
+  <si>
+    <t>women</t>
+  </si>
+  <si>
+    <t>foot</t>
+  </si>
+  <si>
+    <t>feet</t>
+  </si>
+  <si>
+    <t>tooth</t>
+  </si>
+  <si>
+    <t>teeth</t>
+  </si>
+  <si>
+    <t>geese</t>
+  </si>
+  <si>
+    <t>mouse</t>
+  </si>
+  <si>
+    <t>mice</t>
+  </si>
+  <si>
+    <t>louse</t>
+  </si>
+  <si>
+    <t>lice.</t>
+  </si>
+  <si>
+    <t>Ox</t>
+  </si>
+  <si>
+    <t>oxen</t>
+  </si>
+  <si>
+    <t>children.</t>
+  </si>
+  <si>
+    <t>Swine (remain same)</t>
+  </si>
+  <si>
+    <t>Sheep (remain same)</t>
+  </si>
+  <si>
+    <t>Deer (remain same)</t>
+  </si>
+  <si>
+    <t>Cod (remain same)</t>
+  </si>
+  <si>
+    <t>Trout (remain same)</t>
+  </si>
+  <si>
+    <t>Salmon (remain same)</t>
+  </si>
+  <si>
+    <t>Aircraft (remain same)</t>
+  </si>
+  <si>
+    <t>Spacecraft (remain same)</t>
+  </si>
+  <si>
+    <t>Series (remain same)</t>
+  </si>
+  <si>
+    <t>Species (remain same)</t>
+  </si>
+  <si>
+    <t>Pair (remain same)</t>
+  </si>
+  <si>
+    <t>Dozen (remain same)</t>
+  </si>
+  <si>
+    <t>Score (remain same)</t>
+  </si>
+  <si>
+    <t>Gross (remain same)</t>
+  </si>
+  <si>
+    <t>Hundred (remain same)</t>
+  </si>
+  <si>
+    <t>Thousand (remain same)</t>
+  </si>
+  <si>
+    <t>Change Singular to Plural (or otherwise mentioned)</t>
+  </si>
+  <si>
+    <t>Bellows (plural to singular)</t>
+  </si>
+  <si>
+    <t>Scissors (plural to singular)</t>
+  </si>
+  <si>
+    <t>Tongs (plural to singular)</t>
+  </si>
+  <si>
+    <t>Pincers (plural to singular)</t>
+  </si>
+  <si>
+    <t>spectacles (plural to singular)</t>
+  </si>
+  <si>
+    <t>(2) Names of certain articles of dress; as, (plural to singular)</t>
+  </si>
+  <si>
+    <t>Trousers (plural to singular)</t>
+  </si>
+  <si>
+    <t>Drawers (plural to singular)</t>
+  </si>
+  <si>
+    <t>Breeches (plural to singular)</t>
+  </si>
+  <si>
+    <t>Jeans (plural to singular)</t>
+  </si>
+  <si>
+    <t>Tights (plural to singular)</t>
+  </si>
+  <si>
+    <t>Shorts (plural to singular)</t>
+  </si>
+  <si>
+    <t>pyjamas (plural to singular)</t>
+  </si>
+  <si>
+    <t>always used as plural</t>
+  </si>
+  <si>
+    <t>Annals (plural to singular)</t>
+  </si>
+  <si>
+    <t>Thanks (plural to singular)</t>
+  </si>
+  <si>
+    <t>proceeds (of a sale) (plural to singular)</t>
+  </si>
+  <si>
+    <t>tidings (plural to singular)</t>
+  </si>
+  <si>
+    <t>environs (plural to singular)</t>
+  </si>
+  <si>
+    <t>nuptials (plural to singular)</t>
+  </si>
+  <si>
+    <t>obsequies (plural to singular)</t>
+  </si>
+  <si>
+    <t>assets (plural to singular)</t>
+  </si>
+  <si>
+    <t>chatels. (plural to singular)</t>
+  </si>
+  <si>
+    <t>Commander-in-chief</t>
+  </si>
+  <si>
+    <t>commanders-in-chief</t>
+  </si>
+  <si>
+    <t>Coat-of-mail</t>
+  </si>
+  <si>
+    <t>coats-of-mail</t>
+  </si>
+  <si>
+    <t>Son-in-Law</t>
+  </si>
+  <si>
+    <t>sons-in-law</t>
   </si>
 </sst>
 </file>
@@ -7030,9 +7937,1286 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="27.5703125" style="14" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="49" style="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="14"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>798</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="14" t="s">
+        <v>608</v>
+      </c>
+      <c r="B2" s="14" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="14" t="s">
+        <v>609</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="14" t="s">
+        <v>674</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="14" t="s">
+        <v>610</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>611</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
+        <v>612</v>
+      </c>
+      <c r="B7" s="14" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="14" t="s">
+        <v>613</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="14" t="s">
+        <v>614</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="14" t="s">
+        <v>615</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="14" t="s">
+        <v>616</v>
+      </c>
+      <c r="B11" s="14" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="14" t="s">
+        <v>797</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="14" t="s">
+        <v>617</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>618</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="14" t="s">
+        <v>619</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>620</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
+        <v>621</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
+        <v>622</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
+        <v>623</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
+        <v>624</v>
+      </c>
+      <c r="B20" s="14" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
+        <v>625</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
+        <v>626</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
+        <v>627</v>
+      </c>
+      <c r="B23" s="14" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
+        <v>628</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>629</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
+        <v>630</v>
+      </c>
+      <c r="B26" s="14" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>631</v>
+      </c>
+      <c r="B27" s="14" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>632</v>
+      </c>
+      <c r="B28" s="14" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
+        <v>633</v>
+      </c>
+      <c r="B29" s="14" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>634</v>
+      </c>
+      <c r="B30" s="14" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
+        <v>635</v>
+      </c>
+      <c r="B31" s="14" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
+        <v>636</v>
+      </c>
+      <c r="B32" s="14" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
+        <v>637</v>
+      </c>
+      <c r="B33" s="14" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="14" t="s">
+        <v>638</v>
+      </c>
+      <c r="B34" s="14" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="14" t="s">
+        <v>639</v>
+      </c>
+      <c r="B35" s="14" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>640</v>
+      </c>
+      <c r="B36" s="14" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>641</v>
+      </c>
+      <c r="B37" s="14" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>642</v>
+      </c>
+      <c r="B38" s="14" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>643</v>
+      </c>
+      <c r="B39" s="14" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>644</v>
+      </c>
+      <c r="B40" s="14" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B41" s="14" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>645</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="14" t="s">
+        <v>646</v>
+      </c>
+      <c r="B43" s="14" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="14" t="s">
+        <v>647</v>
+      </c>
+      <c r="B44" s="14" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="14" t="s">
+        <v>648</v>
+      </c>
+      <c r="B45" s="14" t="s">
+        <v>719</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="14" t="s">
+        <v>649</v>
+      </c>
+      <c r="B46" s="14" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>650</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>721</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>651</v>
+      </c>
+      <c r="B48" s="14" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
+        <v>652</v>
+      </c>
+      <c r="B49" s="14" t="s">
+        <v>723</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="14" t="s">
+        <v>653</v>
+      </c>
+      <c r="B50" s="14" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="14" t="s">
+        <v>654</v>
+      </c>
+      <c r="B51" s="14" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="14" t="s">
+        <v>655</v>
+      </c>
+      <c r="B52" s="14" t="s">
+        <v>726</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="14" t="s">
+        <v>656</v>
+      </c>
+      <c r="B53" s="14" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="14" t="s">
+        <v>657</v>
+      </c>
+      <c r="B54" s="14" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="14" t="s">
+        <v>658</v>
+      </c>
+      <c r="B55" s="14" t="s">
+        <v>729</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="14" t="s">
+        <v>659</v>
+      </c>
+      <c r="B56" s="14" t="s">
+        <v>730</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="14" t="s">
+        <v>660</v>
+      </c>
+      <c r="B57" s="14" t="s">
+        <v>731</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="14" t="s">
+        <v>661</v>
+      </c>
+      <c r="B58" s="14" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="14" t="s">
+        <v>662</v>
+      </c>
+      <c r="B59" s="14" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="14" t="s">
+        <v>663</v>
+      </c>
+      <c r="B60" s="14" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="14" t="s">
+        <v>669</v>
+      </c>
+      <c r="B61" s="14" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="14" t="s">
+        <v>670</v>
+      </c>
+      <c r="B62" s="14" t="s">
+        <v>735</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="14" t="s">
+        <v>673</v>
+      </c>
+      <c r="B63" s="14" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="14" t="s">
+        <v>671</v>
+      </c>
+      <c r="B64" s="14" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="14" t="s">
+        <v>672</v>
+      </c>
+      <c r="B65" s="14" t="s">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="14" t="s">
+        <v>664</v>
+      </c>
+      <c r="B66" s="14" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="14" t="s">
+        <v>665</v>
+      </c>
+      <c r="B67" s="14" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="14" t="s">
+        <v>666</v>
+      </c>
+      <c r="B68" s="14" t="s">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="14" t="s">
+        <v>667</v>
+      </c>
+      <c r="B69" s="14" t="s">
+        <v>742</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="14" t="s">
+        <v>668</v>
+      </c>
+      <c r="B70" s="14" t="s">
+        <v>743</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B70"/>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Index!A1" display="Positive"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B85"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="22.7109375" style="17" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" style="17" bestFit="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="17"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="22" customFormat="1" ht="45" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>792</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="17" t="s">
+        <v>745</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="17" t="s">
+        <v>747</v>
+      </c>
+      <c r="B3" s="17" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="17" t="s">
+        <v>476</v>
+      </c>
+      <c r="B4" s="17" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="17" t="s">
+        <v>478</v>
+      </c>
+      <c r="B5" s="17" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="17" t="s">
+        <v>748</v>
+      </c>
+      <c r="B6" s="17" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="17" t="s">
+        <v>749</v>
+      </c>
+      <c r="B7" s="17" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="17" t="s">
+        <v>482</v>
+      </c>
+      <c r="B8" s="17" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="17" t="s">
+        <v>484</v>
+      </c>
+      <c r="B9" s="17" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="17" t="s">
+        <v>486</v>
+      </c>
+      <c r="B10" s="17" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="17" t="s">
+        <v>488</v>
+      </c>
+      <c r="B11" s="17" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="17" t="s">
+        <v>5</v>
+      </c>
+      <c r="B12" s="17" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="17" t="s">
+        <v>491</v>
+      </c>
+      <c r="B13" s="17" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="17" t="s">
+        <v>761</v>
+      </c>
+      <c r="B14" s="17" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="17" t="s">
+        <v>493</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="17" t="s">
+        <v>762</v>
+      </c>
+      <c r="B16" s="17" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="17" t="s">
+        <v>751</v>
+      </c>
+      <c r="B17" s="17" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="17" t="s">
+        <v>752</v>
+      </c>
+      <c r="B18" s="17" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="17" t="s">
+        <v>498</v>
+      </c>
+      <c r="B19" s="17" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="17" t="s">
+        <v>753</v>
+      </c>
+      <c r="B20" s="17" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B21" s="17" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="17" t="s">
+        <v>754</v>
+      </c>
+      <c r="B22" s="17" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="17" t="s">
+        <v>503</v>
+      </c>
+      <c r="B23" s="17" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="17" t="s">
+        <v>505</v>
+      </c>
+      <c r="B24" s="17" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="17" t="s">
+        <v>507</v>
+      </c>
+      <c r="B25" s="17" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="17" t="s">
+        <v>509</v>
+      </c>
+      <c r="B26" s="17" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="17" t="s">
+        <v>511</v>
+      </c>
+      <c r="B27" s="17" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="17" t="s">
+        <v>513</v>
+      </c>
+      <c r="B28" s="17" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="17" t="s">
+        <v>515</v>
+      </c>
+      <c r="B29" s="17" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="17" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="17" t="s">
+        <v>517</v>
+      </c>
+      <c r="B31" s="17" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="17" t="s">
+        <v>521</v>
+      </c>
+      <c r="B32" s="17" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="17" t="s">
+        <v>519</v>
+      </c>
+      <c r="B33" s="17" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="17" t="s">
+        <v>525</v>
+      </c>
+      <c r="B34" s="17" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="17" t="s">
+        <v>523</v>
+      </c>
+      <c r="B35" s="17" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="17" t="s">
+        <v>528</v>
+      </c>
+      <c r="B36" s="17" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="17" t="s">
+        <v>533</v>
+      </c>
+      <c r="B37" s="17" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="17" t="s">
+        <v>763</v>
+      </c>
+      <c r="B38" s="17" t="s">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="17" t="s">
+        <v>756</v>
+      </c>
+      <c r="B39" s="17" t="s">
+        <v>757</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="17" t="s">
+        <v>531</v>
+      </c>
+      <c r="B40" s="17" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="17" t="s">
+        <v>764</v>
+      </c>
+      <c r="B41" s="17" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="B42" s="17" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="17" t="s">
+        <v>195</v>
+      </c>
+      <c r="B43" s="17" t="s">
+        <v>758</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="17" t="s">
+        <v>537</v>
+      </c>
+      <c r="B44" s="17" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="17" t="s">
+        <v>759</v>
+      </c>
+      <c r="B45" s="17" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="17" t="s">
+        <v>539</v>
+      </c>
+      <c r="B46" s="17" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="17" t="s">
+        <v>541</v>
+      </c>
+      <c r="B47" s="17" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="17" t="s">
+        <v>543</v>
+      </c>
+      <c r="B48" s="17" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="17" t="s">
+        <v>545</v>
+      </c>
+      <c r="B49" s="17" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="17" t="s">
+        <v>546</v>
+      </c>
+      <c r="B50" s="17" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="17" t="s">
+        <v>548</v>
+      </c>
+      <c r="B51" s="17" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="17" t="s">
+        <v>549</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="17" t="s">
+        <v>551</v>
+      </c>
+      <c r="B53" s="17" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="17" t="s">
+        <v>552</v>
+      </c>
+      <c r="B54" s="17" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="17" t="s">
+        <v>554</v>
+      </c>
+      <c r="B56" s="17" t="s">
+        <v>555</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="17" t="s">
+        <v>556</v>
+      </c>
+      <c r="B57" s="17" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="17" t="s">
+        <v>562</v>
+      </c>
+      <c r="B58" s="17" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="17" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="17" t="s">
+        <v>565</v>
+      </c>
+      <c r="B60" s="17" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="17" t="s">
+        <v>566</v>
+      </c>
+      <c r="B61" s="17" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="17" t="s">
+        <v>568</v>
+      </c>
+      <c r="B62" s="17" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="17" t="s">
+        <v>570</v>
+      </c>
+      <c r="B63" s="17" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="17" t="s">
+        <v>571</v>
+      </c>
+      <c r="B64" s="17" t="s">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="17" t="s">
+        <v>573</v>
+      </c>
+      <c r="B65" s="17" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="17" t="s">
+        <v>194</v>
+      </c>
+      <c r="B66" s="17" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B67" s="17" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="17" t="s">
+        <v>578</v>
+      </c>
+      <c r="B68" s="17" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="17" t="s">
+        <v>580</v>
+      </c>
+      <c r="B69" s="17" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="17" t="s">
+        <v>581</v>
+      </c>
+      <c r="B70" s="17" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="17" t="s">
+        <v>583</v>
+      </c>
+      <c r="B71" s="17" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="17" t="s">
+        <v>584</v>
+      </c>
+      <c r="B72" s="17" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A73" s="17" t="s">
+        <v>586</v>
+      </c>
+      <c r="B73" s="17" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="17" t="s">
+        <v>535</v>
+      </c>
+      <c r="B74" s="17" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="17" t="s">
+        <v>588</v>
+      </c>
+      <c r="B75" s="17" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="B76" s="17" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="B77" s="17" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="17" t="s">
+        <v>592</v>
+      </c>
+      <c r="B78" s="17" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="17" t="s">
+        <v>596</v>
+      </c>
+      <c r="B79" s="17" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="B80" s="17" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A81" s="17" t="s">
+        <v>604</v>
+      </c>
+      <c r="B81" s="17" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="17" t="s">
+        <v>594</v>
+      </c>
+      <c r="B82" s="17" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="17" t="s">
+        <v>598</v>
+      </c>
+      <c r="B83" s="17" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A84" s="17" t="s">
+        <v>602</v>
+      </c>
+      <c r="B84" s="17" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" s="17" t="s">
+        <v>606</v>
+      </c>
+      <c r="B85" s="17" t="s">
+        <v>607</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A1" location="Index!A1" display="Noun / Verb / Adjective"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B87"/>
+  <dimension ref="A1:B93"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="44.85546875" bestFit="1" customWidth="1"/>
@@ -7048,161 +9232,146 @@
         <v>984</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
-        <v>989</v>
-      </c>
-      <c r="B2" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="26" t="s">
-        <v>745</v>
-      </c>
-      <c r="B3" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="26" t="s">
-        <v>992</v>
-      </c>
-      <c r="B4" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
-        <v>994</v>
-      </c>
-      <c r="B5" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
-        <v>996</v>
-      </c>
-      <c r="B6" t="s">
-        <v>997</v>
+    <row r="2" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="29" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="30" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="30" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29" t="s">
+        <v>1149</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="26" t="s">
-        <v>998</v>
+        <v>989</v>
       </c>
       <c r="B7" t="s">
-        <v>999</v>
+        <v>990</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="26" t="s">
-        <v>1000</v>
+        <v>745</v>
       </c>
       <c r="B8" t="s">
-        <v>1001</v>
+        <v>991</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="26" t="s">
-        <v>1002</v>
+        <v>992</v>
       </c>
       <c r="B9" t="s">
-        <v>1003</v>
+        <v>993</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="26" t="s">
-        <v>1004</v>
+        <v>994</v>
       </c>
       <c r="B10" t="s">
-        <v>1005</v>
+        <v>995</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="26" t="s">
-        <v>1006</v>
+        <v>996</v>
       </c>
       <c r="B11" t="s">
-        <v>1007</v>
+        <v>997</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="26" t="s">
-        <v>1008</v>
+        <v>998</v>
       </c>
       <c r="B12" t="s">
-        <v>1009</v>
+        <v>999</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="26" t="s">
-        <v>1010</v>
+        <v>1000</v>
       </c>
       <c r="B13" t="s">
-        <v>1011</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
-        <v>1012</v>
+        <v>1002</v>
       </c>
       <c r="B14" t="s">
-        <v>323</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="26" t="s">
-        <v>1013</v>
+        <v>1004</v>
       </c>
       <c r="B15" t="s">
-        <v>1014</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="26" t="s">
-        <v>1015</v>
+        <v>1006</v>
       </c>
       <c r="B16" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="26" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
       <c r="B17" t="s">
-        <v>1018</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="26" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
       <c r="B18" t="s">
-        <v>1020</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="26" t="s">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="B19" t="s">
-        <v>1022</v>
+        <v>323</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="26" t="s">
-        <v>533</v>
+        <v>1013</v>
       </c>
       <c r="B20" t="s">
-        <v>1023</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
-        <v>1024</v>
+        <v>1015</v>
       </c>
       <c r="B21" t="s">
         <v>1016</v>
@@ -7210,523 +9379,568 @@
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="26" t="s">
-        <v>764</v>
+        <v>1017</v>
       </c>
       <c r="B22" t="s">
-        <v>435</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="26" t="s">
-        <v>1025</v>
+        <v>1019</v>
       </c>
       <c r="B23" t="s">
-        <v>1026</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="26" t="s">
-        <v>1027</v>
+        <v>1021</v>
       </c>
       <c r="B24" t="s">
-        <v>1028</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="26" t="s">
-        <v>1029</v>
+        <v>533</v>
       </c>
       <c r="B25" t="s">
-        <v>1030</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="26" t="s">
-        <v>1031</v>
+        <v>1024</v>
       </c>
       <c r="B26" t="s">
-        <v>1032</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="26" t="s">
-        <v>1033</v>
+        <v>764</v>
       </c>
       <c r="B27" t="s">
-        <v>1034</v>
+        <v>435</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="26" t="s">
-        <v>1035</v>
+        <v>1025</v>
       </c>
       <c r="B28" t="s">
-        <v>1036</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="26" t="s">
-        <v>1037</v>
+        <v>1027</v>
       </c>
       <c r="B29" t="s">
-        <v>1038</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="26" t="s">
-        <v>1039</v>
+        <v>1029</v>
       </c>
       <c r="B30" t="s">
-        <v>1040</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="26" t="s">
-        <v>1041</v>
+        <v>1031</v>
       </c>
       <c r="B31" t="s">
-        <v>1042</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="26" t="s">
-        <v>1043</v>
+        <v>1033</v>
       </c>
       <c r="B32" t="s">
-        <v>1044</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" s="26" t="s">
-        <v>1045</v>
+        <v>1035</v>
       </c>
       <c r="B33" t="s">
-        <v>1046</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" s="26" t="s">
-        <v>1047</v>
+        <v>1037</v>
       </c>
       <c r="B34" t="s">
-        <v>1011</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" s="26" t="s">
-        <v>1048</v>
+        <v>1039</v>
       </c>
       <c r="B35" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" s="26" t="s">
-        <v>1050</v>
+        <v>1041</v>
       </c>
       <c r="B36" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="26" t="s">
-        <v>1052</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1053</v>
+        <v>1042</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="30" t="s">
+        <v>1150</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" s="26" t="s">
-        <v>1054</v>
+        <v>1043</v>
       </c>
       <c r="B38" t="s">
-        <v>1055</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" s="26" t="s">
-        <v>1056</v>
+        <v>1045</v>
       </c>
       <c r="B39" t="s">
-        <v>1057</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" s="26" t="s">
-        <v>1058</v>
+        <v>1047</v>
       </c>
       <c r="B40" t="s">
-        <v>1059</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" s="26" t="s">
-        <v>1060</v>
+        <v>1048</v>
       </c>
       <c r="B41" t="s">
-        <v>1061</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" s="26" t="s">
-        <v>985</v>
+        <v>1050</v>
       </c>
       <c r="B42" t="s">
-        <v>986</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" s="26" t="s">
-        <v>1062</v>
+        <v>1052</v>
       </c>
       <c r="B43" t="s">
-        <v>1063</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" s="26" t="s">
-        <v>1064</v>
+        <v>1054</v>
       </c>
       <c r="B44" t="s">
-        <v>1065</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" s="26" t="s">
-        <v>1066</v>
+        <v>1056</v>
       </c>
       <c r="B45" t="s">
-        <v>1067</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" s="26" t="s">
-        <v>1068</v>
+        <v>1058</v>
       </c>
       <c r="B46" t="s">
-        <v>1069</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" s="26" t="s">
-        <v>1070</v>
+        <v>1060</v>
       </c>
       <c r="B47" t="s">
-        <v>1071</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" s="26" t="s">
-        <v>1072</v>
+        <v>985</v>
       </c>
       <c r="B48" t="s">
-        <v>1073</v>
+        <v>986</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" s="26" t="s">
-        <v>1074</v>
+        <v>1062</v>
       </c>
       <c r="B49" t="s">
-        <v>1075</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="29" t="s">
-        <v>987</v>
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="26" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1065</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" s="26" t="s">
-        <v>1076</v>
+        <v>1066</v>
       </c>
       <c r="B51" t="s">
-        <v>1077</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" s="26" t="s">
-        <v>1078</v>
+        <v>1068</v>
       </c>
       <c r="B52" t="s">
-        <v>1079</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" s="26" t="s">
-        <v>1080</v>
+        <v>1070</v>
       </c>
       <c r="B53" t="s">
-        <v>1081</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" s="26" t="s">
-        <v>1082</v>
+        <v>1072</v>
       </c>
       <c r="B54" t="s">
-        <v>1083</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" s="26" t="s">
-        <v>1084</v>
+        <v>1074</v>
       </c>
       <c r="B55" t="s">
-        <v>1085</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="26" t="s">
-        <v>1086</v>
-      </c>
-      <c r="B56" t="s">
-        <v>1087</v>
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="29" t="s">
+        <v>987</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="26" t="s">
-        <v>1088</v>
+        <v>1076</v>
       </c>
       <c r="B57" t="s">
-        <v>1089</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="26" t="s">
-        <v>1090</v>
+        <v>1078</v>
       </c>
       <c r="B58" t="s">
-        <v>1091</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="26" t="s">
-        <v>1092</v>
+        <v>1080</v>
       </c>
       <c r="B59" t="s">
-        <v>1093</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="26" t="s">
-        <v>1094</v>
+        <v>1082</v>
       </c>
       <c r="B60" t="s">
-        <v>1095</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" s="26" t="s">
-        <v>1096</v>
+        <v>1084</v>
       </c>
       <c r="B61" t="s">
-        <v>1097</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="26" t="s">
-        <v>1098</v>
+        <v>1086</v>
       </c>
       <c r="B62" t="s">
-        <v>1099</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" s="26" t="s">
-        <v>1100</v>
+        <v>1088</v>
       </c>
       <c r="B63" t="s">
-        <v>1101</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" s="26" t="s">
-        <v>1102</v>
+        <v>1090</v>
       </c>
       <c r="B64" t="s">
-        <v>1103</v>
+        <v>1091</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" s="26" t="s">
-        <v>1104</v>
+        <v>1092</v>
       </c>
       <c r="B65" t="s">
-        <v>1105</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" s="26" t="s">
-        <v>1106</v>
+        <v>1094</v>
       </c>
       <c r="B66" t="s">
-        <v>1107</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" s="26" t="s">
-        <v>1108</v>
+        <v>1096</v>
       </c>
       <c r="B67" t="s">
-        <v>1109</v>
+        <v>1097</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" s="26" t="s">
-        <v>1110</v>
+        <v>1098</v>
       </c>
       <c r="B68" t="s">
-        <v>1111</v>
+        <v>1099</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" s="26" t="s">
-        <v>1112</v>
+        <v>1100</v>
       </c>
       <c r="B69" t="s">
-        <v>1113</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" s="26" t="s">
-        <v>1114</v>
+        <v>1102</v>
       </c>
       <c r="B70" t="s">
-        <v>1115</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" s="26" t="s">
-        <v>1116</v>
+        <v>1104</v>
       </c>
       <c r="B71" t="s">
-        <v>1117</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" s="26" t="s">
-        <v>1118</v>
+        <v>1106</v>
       </c>
       <c r="B72" t="s">
-        <v>1119</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" s="26" t="s">
-        <v>1120</v>
+        <v>1108</v>
       </c>
       <c r="B73" t="s">
-        <v>1121</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" s="26" t="s">
-        <v>1122</v>
+        <v>1110</v>
       </c>
       <c r="B74" t="s">
-        <v>1123</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" s="26" t="s">
-        <v>1124</v>
+        <v>1112</v>
       </c>
       <c r="B75" t="s">
-        <v>1125</v>
+        <v>1113</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" s="26" t="s">
-        <v>1126</v>
+        <v>1114</v>
       </c>
       <c r="B76" t="s">
-        <v>1127</v>
+        <v>1115</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" s="26" t="s">
-        <v>1128</v>
+        <v>1116</v>
       </c>
       <c r="B77" t="s">
-        <v>1129</v>
+        <v>1117</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" s="26" t="s">
-        <v>1130</v>
+        <v>1118</v>
       </c>
       <c r="B78" t="s">
-        <v>1131</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="35" t="s">
-        <v>988</v>
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="26" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B79" t="s">
+        <v>1121</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" s="26" t="s">
-        <v>1132</v>
+        <v>1122</v>
       </c>
       <c r="B80" t="s">
-        <v>1133</v>
+        <v>1123</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" s="26" t="s">
-        <v>1134</v>
+        <v>1124</v>
       </c>
       <c r="B81" t="s">
-        <v>1135</v>
+        <v>1125</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" s="26" t="s">
-        <v>1136</v>
+        <v>1126</v>
       </c>
       <c r="B82" t="s">
-        <v>1137</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" s="26" t="s">
-        <v>1138</v>
+        <v>1128</v>
       </c>
       <c r="B83" t="s">
-        <v>1139</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" s="26" t="s">
-        <v>1140</v>
+        <v>1130</v>
       </c>
       <c r="B84" t="s">
-        <v>1141</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="26" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B85" t="s">
-        <v>1143</v>
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="85" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="30" t="s">
+        <v>988</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" s="26" t="s">
-        <v>1144</v>
+        <v>1132</v>
       </c>
       <c r="B86" t="s">
-        <v>1145</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" s="26" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B87" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="26" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B88" t="s">
+        <v>1137</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="26" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B89" t="s">
+        <v>1139</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="26" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B90" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="26" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B91" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="26" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B92" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="26" t="s">
         <v>1146</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B93" t="s">
         <v>1147</v>
       </c>
     </row>
@@ -7736,6 +9950,1602 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B53"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="30.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>1148</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="26" t="s">
+        <v>989</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="26" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1157</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>1158</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>745</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>992</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="26" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1169</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>1096</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1174</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>1130</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1177</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
+        <v>1017</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="26" t="s">
+        <v>1179</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="26" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
+        <v>1187</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="26" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1191</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="26" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1192</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="26" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="26" t="s">
+        <v>1086</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="26" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="26" t="s">
+        <v>1088</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>1054</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="26" t="s">
+        <v>533</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="26" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="26" t="s">
+        <v>1056</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="26" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1201</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="26" t="s">
+        <v>1058</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1202</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="26" t="s">
+        <v>1114</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="26" t="s">
+        <v>1060</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A42" s="26" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1207</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="26" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="26" t="s">
+        <v>1209</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="26" t="s">
+        <v>1064</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="26" t="s">
+        <v>1066</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="26" t="s">
+        <v>1100</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="26" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A49" s="26" t="s">
+        <v>1215</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="26" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
+        <v>1108</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1217</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="26" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1218</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="26" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:B1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B154"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="94.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.42578125" customWidth="1"/>
+    <col min="3" max="3" width="15" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="29" t="s">
+        <v>1420</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="35" t="s">
+        <v>1220</v>
+      </c>
+      <c r="B2" s="35"/>
+    </row>
+    <row r="3" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="35" t="s">
+        <v>1221</v>
+      </c>
+      <c r="B3" s="35"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="26" t="s">
+        <v>745</v>
+      </c>
+      <c r="B4" s="26" t="s">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
+        <v>1276</v>
+      </c>
+      <c r="B5" s="26" t="s">
+        <v>1277</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="26" t="s">
+        <v>1160</v>
+      </c>
+      <c r="B6" s="26" t="s">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="26" t="s">
+        <v>1279</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="26" t="s">
+        <v>1281</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="26" t="s">
+        <v>1165</v>
+      </c>
+      <c r="B9" s="26" t="s">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="35" t="s">
+        <v>1222</v>
+      </c>
+      <c r="B10" s="35"/>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="26" t="s">
+        <v>1284</v>
+      </c>
+      <c r="B11" s="26" t="s">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="26" t="s">
+        <v>1286</v>
+      </c>
+      <c r="B12" s="26" t="s">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="26" t="s">
+        <v>1288</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>1289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="26" t="s">
+        <v>1290</v>
+      </c>
+      <c r="B14" s="26" t="s">
+        <v>1291</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="26" t="s">
+        <v>1292</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>1293</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="26" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B16" s="26" t="s">
+        <v>1295</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="26" t="s">
+        <v>1296</v>
+      </c>
+      <c r="B17" s="26" t="s">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="26" t="s">
+        <v>1298</v>
+      </c>
+      <c r="B18" s="26" t="s">
+        <v>1299</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="26" t="s">
+        <v>1300</v>
+      </c>
+      <c r="B19" s="26" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="35" t="s">
+        <v>1223</v>
+      </c>
+      <c r="B20" s="35"/>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
+        <v>1302</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>1303</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="26" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="26" t="s">
+        <v>1120</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="26" t="s">
+        <v>1307</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="26" t="s">
+        <v>1309</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="26" t="s">
+        <v>1311</v>
+      </c>
+      <c r="B26" s="26" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="26" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B27" s="26" t="s">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="26" t="s">
+        <v>1314</v>
+      </c>
+      <c r="B28" s="26" t="s">
+        <v>1315</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="35" t="s">
+        <v>1224</v>
+      </c>
+      <c r="B29" s="35"/>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="26" t="s">
+        <v>1316</v>
+      </c>
+      <c r="B30" s="26" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="26" t="s">
+        <v>1318</v>
+      </c>
+      <c r="B31" s="26" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="26" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B32" s="26" t="s">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="26" t="s">
+        <v>1322</v>
+      </c>
+      <c r="B33" s="26" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" s="26" t="s">
+        <v>1324</v>
+      </c>
+      <c r="B34" s="26" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="26" t="s">
+        <v>1326</v>
+      </c>
+      <c r="B35" s="26" t="s">
+        <v>1327</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" s="26" t="s">
+        <v>1328</v>
+      </c>
+      <c r="B36" s="26" t="s">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="26" t="s">
+        <v>1330</v>
+      </c>
+      <c r="B37" s="26" t="s">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A38" s="26" t="s">
+        <v>1332</v>
+      </c>
+      <c r="B38" s="26" t="s">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="26" t="s">
+        <v>1334</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="26" t="s">
+        <v>1336</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A41" s="26" t="s">
+        <v>1338</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>1339</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="35" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B42" s="35"/>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="26" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B43" s="26" t="s">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="26" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="26" t="s">
+        <v>1346</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="26" t="s">
+        <v>1348</v>
+      </c>
+      <c r="B46" s="26" t="s">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="26" t="s">
+        <v>1350</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>1351</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="26" t="s">
+        <v>1352</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="35" t="s">
+        <v>1341</v>
+      </c>
+      <c r="B49" s="35"/>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="26" t="s">
+        <v>1354</v>
+      </c>
+      <c r="B50" s="26" t="s">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A51" s="26" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>1356</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="26" t="s">
+        <v>1357</v>
+      </c>
+      <c r="B52" s="26" t="s">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="26" t="s">
+        <v>756</v>
+      </c>
+      <c r="B53" s="26" t="s">
+        <v>1359</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="26" t="s">
+        <v>1360</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="26" t="s">
+        <v>1362</v>
+      </c>
+      <c r="B55" s="26" t="s">
+        <v>1363</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="26" t="s">
+        <v>1364</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A57" s="26" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A58" s="26" t="s">
+        <v>1368</v>
+      </c>
+      <c r="B58" s="26" t="s">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A59" s="26" t="s">
+        <v>1370</v>
+      </c>
+      <c r="B59" s="26" t="s">
+        <v>1371</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A60" s="26" t="s">
+        <v>1372</v>
+      </c>
+      <c r="B60" s="26" t="s">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="26" t="s">
+        <v>1374</v>
+      </c>
+      <c r="B61" s="26" t="s">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="26" t="s">
+        <v>1376</v>
+      </c>
+      <c r="B62" s="26" t="s">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="35" t="s">
+        <v>1225</v>
+      </c>
+      <c r="B63" s="35"/>
+    </row>
+    <row r="64" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="35" t="s">
+        <v>1226</v>
+      </c>
+      <c r="B64" s="35"/>
+    </row>
+    <row r="65" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="35" t="s">
+        <v>1227</v>
+      </c>
+      <c r="B65" s="35"/>
+    </row>
+    <row r="66" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="35" t="s">
+        <v>1342</v>
+      </c>
+      <c r="B66" s="35"/>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A67" s="26" t="s">
+        <v>1378</v>
+      </c>
+      <c r="B67" s="26" t="s">
+        <v>1379</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A68" s="26" t="s">
+        <v>1380</v>
+      </c>
+      <c r="B68" s="26" t="s">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="26" t="s">
+        <v>1382</v>
+      </c>
+      <c r="B69" s="26" t="s">
+        <v>1383</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="26" t="s">
+        <v>1384</v>
+      </c>
+      <c r="B70" s="26" t="s">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="26" t="s">
+        <v>1386</v>
+      </c>
+      <c r="B71" s="26" t="s">
+        <v>1387</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="26" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B72" s="26" t="s">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="35" t="s">
+        <v>1228</v>
+      </c>
+      <c r="B73" s="35"/>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A74" s="26" t="s">
+        <v>290</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A75" s="26" t="s">
+        <v>435</v>
+      </c>
+      <c r="B75" s="26" t="s">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A76" s="26" t="s">
+        <v>1392</v>
+      </c>
+      <c r="B76" s="26" t="s">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A77" s="26" t="s">
+        <v>1394</v>
+      </c>
+      <c r="B77" s="26" t="s">
+        <v>1395</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A78" s="26" t="s">
+        <v>1014</v>
+      </c>
+      <c r="B78" s="26" t="s">
+        <v>1396</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A79" s="26" t="s">
+        <v>1397</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A80" s="26" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="35" t="s">
+        <v>1229</v>
+      </c>
+      <c r="B81" s="35"/>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A82" s="26" t="s">
+        <v>1401</v>
+      </c>
+      <c r="B82" s="26" t="s">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A83" s="26" t="s">
+        <v>476</v>
+      </c>
+      <c r="B83" s="26" t="s">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="84" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="35" t="s">
+        <v>1230</v>
+      </c>
+      <c r="B84" s="35"/>
+    </row>
+    <row r="85" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="35" t="s">
+        <v>1231</v>
+      </c>
+      <c r="B85" s="35"/>
+    </row>
+    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A86" s="26" t="s">
+        <v>1232</v>
+      </c>
+      <c r="B86" s="26" t="s">
+        <v>1404</v>
+      </c>
+    </row>
+    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A87" s="26" t="s">
+        <v>1233</v>
+      </c>
+      <c r="B87" s="26" t="s">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A88" s="26" t="s">
+        <v>1234</v>
+      </c>
+      <c r="B88" s="26" t="s">
+        <v>1406</v>
+      </c>
+    </row>
+    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A89" s="26" t="s">
+        <v>1235</v>
+      </c>
+      <c r="B89" s="26" t="s">
+        <v>1407</v>
+      </c>
+    </row>
+    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A90" s="26" t="s">
+        <v>1236</v>
+      </c>
+      <c r="B90" s="26" t="s">
+        <v>1408</v>
+      </c>
+    </row>
+    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A91" s="26" t="s">
+        <v>1237</v>
+      </c>
+      <c r="B91" s="26" t="s">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A92" s="26" t="s">
+        <v>1238</v>
+      </c>
+      <c r="B92" s="26" t="s">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A93" s="26" t="s">
+        <v>1239</v>
+      </c>
+      <c r="B93" s="26" t="s">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A94" s="26" t="s">
+        <v>1240</v>
+      </c>
+      <c r="B94" s="26" t="s">
+        <v>1412</v>
+      </c>
+    </row>
+    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A95" s="26" t="s">
+        <v>1241</v>
+      </c>
+      <c r="B95" s="26" t="s">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A96" s="26" t="s">
+        <v>1242</v>
+      </c>
+      <c r="B96" s="26" t="s">
+        <v>1414</v>
+      </c>
+    </row>
+    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A97" s="26" t="s">
+        <v>1243</v>
+      </c>
+      <c r="B97" s="26" t="s">
+        <v>1415</v>
+      </c>
+    </row>
+    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A98" s="26" t="s">
+        <v>1244</v>
+      </c>
+      <c r="B98" s="26" t="s">
+        <v>1416</v>
+      </c>
+    </row>
+    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A99" s="26" t="s">
+        <v>1245</v>
+      </c>
+      <c r="B99" s="26" t="s">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A100" s="26" t="s">
+        <v>1246</v>
+      </c>
+      <c r="B100" s="26" t="s">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A101" s="26" t="s">
+        <v>1247</v>
+      </c>
+      <c r="B101" s="26" t="s">
+        <v>1419</v>
+      </c>
+    </row>
+    <row r="102" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A102" s="35" t="s">
+        <v>1248</v>
+      </c>
+      <c r="B102" s="35"/>
+    </row>
+    <row r="103" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="35" t="s">
+        <v>1249</v>
+      </c>
+      <c r="B103" s="35"/>
+    </row>
+    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A104" s="26" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B104" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A105" s="26" t="s">
+        <v>1422</v>
+      </c>
+      <c r="B105" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A106" s="26" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B106" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A107" s="26" t="s">
+        <v>1424</v>
+      </c>
+      <c r="B107" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A108" s="26" t="s">
+        <v>1425</v>
+      </c>
+      <c r="B108" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A109" s="26" t="s">
+        <v>1426</v>
+      </c>
+      <c r="B109" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A110" s="26" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B110" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A111" s="26" t="s">
+        <v>1428</v>
+      </c>
+      <c r="B111" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A112" s="26" t="s">
+        <v>1429</v>
+      </c>
+      <c r="B112" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A113" s="26" t="s">
+        <v>1430</v>
+      </c>
+      <c r="B113" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A114" s="26" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B114" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A115" s="26" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B115" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A116" s="26" t="s">
+        <v>1433</v>
+      </c>
+      <c r="B116" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A117" s="35" t="s">
+        <v>1250</v>
+      </c>
+      <c r="B117" s="35"/>
+    </row>
+    <row r="118" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A118" s="26" t="s">
+        <v>1435</v>
+      </c>
+      <c r="B118" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A119" s="26" t="s">
+        <v>1436</v>
+      </c>
+      <c r="B119" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A120" s="26" t="s">
+        <v>1437</v>
+      </c>
+      <c r="B120" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A121" s="26" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B121" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A122" s="26" t="s">
+        <v>1439</v>
+      </c>
+      <c r="B122" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A123" s="26" t="s">
+        <v>1440</v>
+      </c>
+      <c r="B123" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A124" s="26" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B124" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A125" s="26" t="s">
+        <v>1442</v>
+      </c>
+      <c r="B125" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A126" s="26" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B126" s="26" t="s">
+        <v>1434</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A127" s="35" t="s">
+        <v>1251</v>
+      </c>
+      <c r="B127" s="35"/>
+    </row>
+    <row r="128" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A128" s="35" t="s">
+        <v>1252</v>
+      </c>
+      <c r="B128" s="35"/>
+    </row>
+    <row r="129" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="35" t="s">
+        <v>1253</v>
+      </c>
+      <c r="B129" s="35"/>
+    </row>
+    <row r="130" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A130" s="35" t="s">
+        <v>1254</v>
+      </c>
+      <c r="B130" s="35"/>
+    </row>
+    <row r="131" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A131" s="35" t="s">
+        <v>1255</v>
+      </c>
+      <c r="B131" s="35"/>
+    </row>
+    <row r="132" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A132" s="35" t="s">
+        <v>1256</v>
+      </c>
+      <c r="B132" s="35"/>
+    </row>
+    <row r="133" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A133" s="35" t="s">
+        <v>1257</v>
+      </c>
+      <c r="B133" s="35"/>
+    </row>
+    <row r="134" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A134" s="35" t="s">
+        <v>1258</v>
+      </c>
+      <c r="B134" s="35"/>
+    </row>
+    <row r="135" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A135" s="35" t="s">
+        <v>1259</v>
+      </c>
+      <c r="B135" s="35"/>
+    </row>
+    <row r="136" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="35" t="s">
+        <v>1260</v>
+      </c>
+      <c r="B136" s="35"/>
+    </row>
+    <row r="137" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A137" s="35" t="s">
+        <v>1261</v>
+      </c>
+      <c r="B137" s="35"/>
+    </row>
+    <row r="138" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A138" s="35"/>
+      <c r="B138" s="35"/>
+    </row>
+    <row r="139" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="35" t="s">
+        <v>1262</v>
+      </c>
+      <c r="B139" s="35"/>
+    </row>
+    <row r="140" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A140" s="35" t="s">
+        <v>1263</v>
+      </c>
+      <c r="B140" s="35"/>
+    </row>
+    <row r="141" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A141" s="35" t="s">
+        <v>1264</v>
+      </c>
+      <c r="B141" s="35"/>
+    </row>
+    <row r="142" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A142" s="35" t="s">
+        <v>1265</v>
+      </c>
+      <c r="B142" s="35"/>
+    </row>
+    <row r="143" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A143" s="35" t="s">
+        <v>1266</v>
+      </c>
+      <c r="B143" s="35"/>
+    </row>
+    <row r="144" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A144" s="35" t="s">
+        <v>1267</v>
+      </c>
+      <c r="B144" s="35"/>
+    </row>
+    <row r="145" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A145" s="35" t="s">
+        <v>1268</v>
+      </c>
+      <c r="B145" s="35"/>
+    </row>
+    <row r="146" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A146" s="35" t="s">
+        <v>1269</v>
+      </c>
+      <c r="B146" s="35"/>
+    </row>
+    <row r="147" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="35" t="s">
+        <v>1270</v>
+      </c>
+      <c r="B147" s="35"/>
+    </row>
+    <row r="148" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A148" s="35" t="s">
+        <v>1271</v>
+      </c>
+      <c r="B148" s="35"/>
+    </row>
+    <row r="149" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A149" s="35" t="s">
+        <v>1272</v>
+      </c>
+      <c r="B149" s="35"/>
+    </row>
+    <row r="150" spans="1:2" s="18" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="35" t="s">
+        <v>1273</v>
+      </c>
+      <c r="B150" s="35"/>
+    </row>
+    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A151" s="26" t="s">
+        <v>1444</v>
+      </c>
+      <c r="B151" s="26" t="s">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A152" s="26" t="s">
+        <v>1446</v>
+      </c>
+      <c r="B152" s="26" t="s">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A153" s="26" t="s">
+        <v>1448</v>
+      </c>
+      <c r="B153" s="26" t="s">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B154" s="26"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B135"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8782,7 +12592,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8943,7 +12753,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -9192,7 +13002,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C104"/>
   <sheetFormatPr defaultColWidth="62.85546875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10036,7 +13846,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -10571,1281 +14381,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="27.5703125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="49" style="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="14"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
-        <v>798</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
-        <v>608</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>676</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="14" t="s">
-        <v>609</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>677</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="14" t="s">
-        <v>674</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="14" t="s">
-        <v>610</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>679</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="14" t="s">
-        <v>611</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="14" t="s">
-        <v>612</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="14" t="s">
-        <v>613</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="14" t="s">
-        <v>614</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>683</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="14" t="s">
-        <v>615</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="14" t="s">
-        <v>616</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="14" t="s">
-        <v>797</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="14" t="s">
-        <v>617</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>687</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>618</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>619</v>
-      </c>
-      <c r="B15" s="14" t="s">
-        <v>689</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="14" t="s">
-        <v>620</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="14" t="s">
-        <v>621</v>
-      </c>
-      <c r="B17" s="14" t="s">
-        <v>691</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="14" t="s">
-        <v>622</v>
-      </c>
-      <c r="B18" s="14" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="14" t="s">
-        <v>623</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="14" t="s">
-        <v>624</v>
-      </c>
-      <c r="B20" s="14" t="s">
-        <v>694</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="14" t="s">
-        <v>625</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>695</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="14" t="s">
-        <v>626</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>696</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="14" t="s">
-        <v>627</v>
-      </c>
-      <c r="B23" s="14" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="14" t="s">
-        <v>628</v>
-      </c>
-      <c r="B24" s="14" t="s">
-        <v>698</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="14" t="s">
-        <v>629</v>
-      </c>
-      <c r="B25" s="14" t="s">
-        <v>699</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>630</v>
-      </c>
-      <c r="B26" s="14" t="s">
-        <v>700</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="14" t="s">
-        <v>631</v>
-      </c>
-      <c r="B27" s="14" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>632</v>
-      </c>
-      <c r="B28" s="14" t="s">
-        <v>702</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>633</v>
-      </c>
-      <c r="B29" s="14" t="s">
-        <v>703</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>634</v>
-      </c>
-      <c r="B30" s="14" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="14" t="s">
-        <v>635</v>
-      </c>
-      <c r="B31" s="14" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
-        <v>636</v>
-      </c>
-      <c r="B32" s="14" t="s">
-        <v>706</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="14" t="s">
-        <v>637</v>
-      </c>
-      <c r="B33" s="14" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="14" t="s">
-        <v>638</v>
-      </c>
-      <c r="B34" s="14" t="s">
-        <v>708</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="14" t="s">
-        <v>639</v>
-      </c>
-      <c r="B35" s="14" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
-        <v>640</v>
-      </c>
-      <c r="B36" s="14" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>641</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>711</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>642</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>712</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
-        <v>643</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="14" t="s">
-        <v>644</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>714</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>715</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
-        <v>645</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>716</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="14" t="s">
-        <v>646</v>
-      </c>
-      <c r="B43" s="14" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="14" t="s">
-        <v>647</v>
-      </c>
-      <c r="B44" s="14" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="14" t="s">
-        <v>648</v>
-      </c>
-      <c r="B45" s="14" t="s">
-        <v>719</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="14" t="s">
-        <v>649</v>
-      </c>
-      <c r="B46" s="14" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
-        <v>650</v>
-      </c>
-      <c r="B47" s="14" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
-        <v>651</v>
-      </c>
-      <c r="B48" s="14" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="14" t="s">
-        <v>652</v>
-      </c>
-      <c r="B49" s="14" t="s">
-        <v>723</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
-        <v>653</v>
-      </c>
-      <c r="B50" s="14" t="s">
-        <v>724</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
-        <v>654</v>
-      </c>
-      <c r="B51" s="14" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="14" t="s">
-        <v>655</v>
-      </c>
-      <c r="B52" s="14" t="s">
-        <v>726</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
-        <v>656</v>
-      </c>
-      <c r="B53" s="14" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="14" t="s">
-        <v>657</v>
-      </c>
-      <c r="B54" s="14" t="s">
-        <v>728</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="14" t="s">
-        <v>658</v>
-      </c>
-      <c r="B55" s="14" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
-        <v>659</v>
-      </c>
-      <c r="B56" s="14" t="s">
-        <v>730</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="14" t="s">
-        <v>660</v>
-      </c>
-      <c r="B57" s="14" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="14" t="s">
-        <v>661</v>
-      </c>
-      <c r="B58" s="14" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
-        <v>662</v>
-      </c>
-      <c r="B59" s="14" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="14" t="s">
-        <v>663</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>733</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="14" t="s">
-        <v>669</v>
-      </c>
-      <c r="B61" s="14" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="14" t="s">
-        <v>670</v>
-      </c>
-      <c r="B62" s="14" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="14" t="s">
-        <v>673</v>
-      </c>
-      <c r="B63" s="14" t="s">
-        <v>736</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="14" t="s">
-        <v>671</v>
-      </c>
-      <c r="B64" s="14" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="14" t="s">
-        <v>672</v>
-      </c>
-      <c r="B65" s="14" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
-        <v>664</v>
-      </c>
-      <c r="B66" s="14" t="s">
-        <v>739</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="14" t="s">
-        <v>665</v>
-      </c>
-      <c r="B67" s="14" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="14" t="s">
-        <v>666</v>
-      </c>
-      <c r="B68" s="14" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="14" t="s">
-        <v>667</v>
-      </c>
-      <c r="B69" s="14" t="s">
-        <v>742</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="14" t="s">
-        <v>668</v>
-      </c>
-      <c r="B70" s="14" t="s">
-        <v>743</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:B70"/>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Index!A1" display="Positive"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B85"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="22.7109375" style="17" customWidth="1"/>
-    <col min="2" max="2" width="15.140625" style="17" bestFit="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="17"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" s="22" customFormat="1" ht="45" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>792</v>
-      </c>
-      <c r="B1" s="22" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>745</v>
-      </c>
-      <c r="B2" s="17" t="s">
-        <v>746</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
-        <v>747</v>
-      </c>
-      <c r="B3" s="17" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
-        <v>476</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
-        <v>478</v>
-      </c>
-      <c r="B5" s="17" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
-        <v>748</v>
-      </c>
-      <c r="B6" s="17" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
-        <v>749</v>
-      </c>
-      <c r="B7" s="17" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
-        <v>482</v>
-      </c>
-      <c r="B8" s="17" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="17" t="s">
-        <v>484</v>
-      </c>
-      <c r="B9" s="17" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
-        <v>486</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
-        <v>488</v>
-      </c>
-      <c r="B11" s="17" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>490</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
-        <v>491</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
-        <v>761</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
-        <v>493</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
-        <v>762</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="17" t="s">
-        <v>751</v>
-      </c>
-      <c r="B17" s="17" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
-        <v>752</v>
-      </c>
-      <c r="B18" s="17" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
-        <v>498</v>
-      </c>
-      <c r="B19" s="17" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A20" s="17" t="s">
-        <v>753</v>
-      </c>
-      <c r="B20" s="17" t="s">
-        <v>500</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A21" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B21" s="17" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
-        <v>754</v>
-      </c>
-      <c r="B22" s="17" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
-        <v>503</v>
-      </c>
-      <c r="B23" s="17" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
-        <v>505</v>
-      </c>
-      <c r="B24" s="17" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A25" s="17" t="s">
-        <v>507</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>508</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A26" s="17" t="s">
-        <v>509</v>
-      </c>
-      <c r="B26" s="17" t="s">
-        <v>510</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A27" s="17" t="s">
-        <v>511</v>
-      </c>
-      <c r="B27" s="17" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A28" s="17" t="s">
-        <v>513</v>
-      </c>
-      <c r="B28" s="17" t="s">
-        <v>514</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
-        <v>515</v>
-      </c>
-      <c r="B29" s="17" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A30" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="17" t="s">
-        <v>755</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A31" s="17" t="s">
-        <v>517</v>
-      </c>
-      <c r="B31" s="17" t="s">
-        <v>518</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A32" s="17" t="s">
-        <v>521</v>
-      </c>
-      <c r="B32" s="17" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A33" s="17" t="s">
-        <v>519</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A34" s="17" t="s">
-        <v>525</v>
-      </c>
-      <c r="B34" s="17" t="s">
-        <v>526</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A35" s="17" t="s">
-        <v>523</v>
-      </c>
-      <c r="B35" s="17" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
-        <v>528</v>
-      </c>
-      <c r="B36" s="17" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A37" s="17" t="s">
-        <v>533</v>
-      </c>
-      <c r="B37" s="17" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
-        <v>763</v>
-      </c>
-      <c r="B38" s="17" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A39" s="17" t="s">
-        <v>756</v>
-      </c>
-      <c r="B39" s="17" t="s">
-        <v>757</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A40" s="17" t="s">
-        <v>531</v>
-      </c>
-      <c r="B40" s="17" t="s">
-        <v>532</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
-        <v>764</v>
-      </c>
-      <c r="B41" s="17" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A42" s="17" t="s">
-        <v>535</v>
-      </c>
-      <c r="B42" s="17" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A43" s="17" t="s">
-        <v>195</v>
-      </c>
-      <c r="B43" s="17" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A44" s="17" t="s">
-        <v>537</v>
-      </c>
-      <c r="B44" s="17" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A45" s="17" t="s">
-        <v>759</v>
-      </c>
-      <c r="B45" s="17" t="s">
-        <v>527</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A46" s="17" t="s">
-        <v>539</v>
-      </c>
-      <c r="B46" s="17" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A47" s="17" t="s">
-        <v>541</v>
-      </c>
-      <c r="B47" s="17" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A48" s="17" t="s">
-        <v>543</v>
-      </c>
-      <c r="B48" s="17" t="s">
-        <v>544</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="17" t="s">
-        <v>545</v>
-      </c>
-      <c r="B49" s="17" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
-        <v>546</v>
-      </c>
-      <c r="B50" s="17" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A51" s="17" t="s">
-        <v>548</v>
-      </c>
-      <c r="B51" s="17" t="s">
-        <v>558</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A52" s="17" t="s">
-        <v>549</v>
-      </c>
-      <c r="B52" s="17" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A53" s="17" t="s">
-        <v>551</v>
-      </c>
-      <c r="B53" s="17" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A54" s="17" t="s">
-        <v>552</v>
-      </c>
-      <c r="B54" s="17" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A55" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="B55" s="17" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A56" s="17" t="s">
-        <v>554</v>
-      </c>
-      <c r="B56" s="17" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A57" s="17" t="s">
-        <v>556</v>
-      </c>
-      <c r="B57" s="17" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A58" s="17" t="s">
-        <v>562</v>
-      </c>
-      <c r="B58" s="17" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A59" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B59" s="17" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A60" s="17" t="s">
-        <v>565</v>
-      </c>
-      <c r="B60" s="17" t="s">
-        <v>547</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A61" s="17" t="s">
-        <v>566</v>
-      </c>
-      <c r="B61" s="17" t="s">
-        <v>567</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="17" t="s">
-        <v>568</v>
-      </c>
-      <c r="B62" s="17" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" s="17" t="s">
-        <v>570</v>
-      </c>
-      <c r="B63" s="17" t="s">
-        <v>574</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" s="17" t="s">
-        <v>571</v>
-      </c>
-      <c r="B64" s="17" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A65" s="17" t="s">
-        <v>573</v>
-      </c>
-      <c r="B65" s="17" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A66" s="17" t="s">
-        <v>194</v>
-      </c>
-      <c r="B66" s="17" t="s">
-        <v>576</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A67" s="17" t="s">
-        <v>196</v>
-      </c>
-      <c r="B67" s="17" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A68" s="17" t="s">
-        <v>578</v>
-      </c>
-      <c r="B68" s="17" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A69" s="17" t="s">
-        <v>580</v>
-      </c>
-      <c r="B69" s="17" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A70" s="17" t="s">
-        <v>581</v>
-      </c>
-      <c r="B70" s="17" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A71" s="17" t="s">
-        <v>583</v>
-      </c>
-      <c r="B71" s="17" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A72" s="17" t="s">
-        <v>584</v>
-      </c>
-      <c r="B72" s="17" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A73" s="17" t="s">
-        <v>586</v>
-      </c>
-      <c r="B73" s="17" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A74" s="17" t="s">
-        <v>535</v>
-      </c>
-      <c r="B74" s="17" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A75" s="17" t="s">
-        <v>588</v>
-      </c>
-      <c r="B75" s="17" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A76" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="B76" s="17" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A77" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="B77" s="17" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A78" s="17" t="s">
-        <v>592</v>
-      </c>
-      <c r="B78" s="17" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A79" s="17" t="s">
-        <v>596</v>
-      </c>
-      <c r="B79" s="17" t="s">
-        <v>597</v>
-      </c>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A80" s="17" t="s">
-        <v>600</v>
-      </c>
-      <c r="B80" s="17" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A81" s="17" t="s">
-        <v>604</v>
-      </c>
-      <c r="B81" s="17" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A82" s="17" t="s">
-        <v>594</v>
-      </c>
-      <c r="B82" s="17" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A83" s="17" t="s">
-        <v>598</v>
-      </c>
-      <c r="B83" s="17" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A84" s="17" t="s">
-        <v>602</v>
-      </c>
-      <c r="B84" s="17" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A85" s="17" t="s">
-        <v>606</v>
-      </c>
-      <c r="B85" s="17" t="s">
-        <v>607</v>
-      </c>
-    </row>
-  </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A1" location="Index!A1" display="Noun / Verb / Adjective"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/question_bank/ENGLISH - Grammer.xlsx
+++ b/question_bank/ENGLISH - Grammer.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7500" firstSheet="8" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="Syllabus" sheetId="26" r:id="rId1"/>
@@ -21,10 +21,12 @@
     <sheet name="Formation of Adjectives" sheetId="25" r:id="rId7"/>
     <sheet name="Adjectives (HSG Ex6)" sheetId="31" r:id="rId8"/>
     <sheet name="Adjectives (HSG Ex7)" sheetId="32" r:id="rId9"/>
-    <sheet name="Article" sheetId="20" r:id="rId10"/>
-    <sheet name="Preposition" sheetId="19" r:id="rId11"/>
-    <sheet name="Conjunction" sheetId="27" r:id="rId12"/>
-    <sheet name="Correct Sentences" sheetId="15" r:id="rId13"/>
+    <sheet name="Article (HSG Ex 23)" sheetId="33" r:id="rId10"/>
+    <sheet name="Article (HSG Ex 24)" sheetId="34" r:id="rId11"/>
+    <sheet name="Article" sheetId="20" r:id="rId12"/>
+    <sheet name="Preposition" sheetId="19" r:id="rId13"/>
+    <sheet name="Conjunction" sheetId="27" r:id="rId14"/>
+    <sheet name="Correct Sentences" sheetId="15" r:id="rId15"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Comparison of Adjectives'!$A$1:$B$70</definedName>
@@ -42,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1670" uniqueCount="1560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1857" uniqueCount="1708">
   <si>
     <t>Anger</t>
   </si>
@@ -7487,6 +7489,450 @@
   </si>
   <si>
     <t>26. complete</t>
+  </si>
+  <si>
+    <t>Complete the following sentences by filling in {a} or {an} or {the} as may be suitable:-</t>
+  </si>
+  <si>
+    <t>Insert Articles where necessary:-</t>
+  </si>
+  <si>
+    <t>Copper is ______ useful metal.</t>
+  </si>
+  <si>
+    <t>He is not ______ honorable man.</t>
+  </si>
+  <si>
+    <t>______ able man has not always a distinguished look.</t>
+  </si>
+  <si>
+    <t>______ reindeer is a native of Norway.</t>
+  </si>
+  <si>
+    <t>Honest men speak ______ truth.</t>
+  </si>
+  <si>
+    <t>Rustum is ______.</t>
+  </si>
+  <si>
+    <t>Do you see ______ blue sky.</t>
+  </si>
+  <si>
+    <t>Varanasi is holy city.</t>
+  </si>
+  <si>
+    <t>Aladdin had ______ wonderful lamp.</t>
+  </si>
+  <si>
+    <t>The world is ______ happy place.</t>
+  </si>
+  <si>
+    <t>He returned after ______ hour.</t>
+  </si>
+  <si>
+    <t>______ school will shortly close for the Puja holidays.</t>
+  </si>
+  <si>
+    <t>_____ sun shines brightly.</t>
+  </si>
+  <si>
+    <t>I first met him ______ year ago.</t>
+  </si>
+  <si>
+    <t>Yesterday ______ European called at my office.</t>
+  </si>
+  <si>
+    <t>Sanskrit is ______ difficult language.</t>
+  </si>
+  <si>
+    <t>______ Ganga is ______ sacred river.</t>
+  </si>
+  <si>
+    <t>______ lion is ______ king of beasts.</t>
+  </si>
+  <si>
+    <t>You are ______ fool to say that.</t>
+  </si>
+  <si>
+    <t>French is ______ easy language.</t>
+  </si>
+  <si>
+    <t>Who is ______ girl sitting there?</t>
+  </si>
+  <si>
+    <t>Which is ______ longest river in India?</t>
+  </si>
+  <si>
+    <t>Rama has come without ______ umbrella.</t>
+  </si>
+  <si>
+    <t>Mumbai is ______ very dear place to live in.</t>
+  </si>
+  <si>
+    <t>She is ______ untidy girl.</t>
+  </si>
+  <si>
+    <t>The children found ______ egg in the nest.</t>
+  </si>
+  <si>
+    <t>I bought horse, ox, and ______ buffalo.</t>
+  </si>
+  <si>
+    <t>If you see him, give him ______ message.</t>
+  </si>
+  <si>
+    <t>English is language of ______ people of England.</t>
+  </si>
+  <si>
+    <t>The guide knows ______ way.</t>
+  </si>
+  <si>
+    <t>Sri Lanka is ______ island.</t>
+  </si>
+  <si>
+    <t>Let us discuss ______ matter seriously.</t>
+  </si>
+  <si>
+    <t>John got ______ best present.</t>
+  </si>
+  <si>
+    <t>Man, thou art ______ animal.</t>
+  </si>
+  <si>
+    <t>India is one of ______ most industrial countries in Asia.</t>
+  </si>
+  <si>
+    <t>He looks as stupid as ______ owl.</t>
+  </si>
+  <si>
+    <t>He is ______ honour to this profession.</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>an</t>
+  </si>
+  <si>
+    <t>An</t>
+  </si>
+  <si>
+    <t>The</t>
+  </si>
+  <si>
+    <t>the</t>
+  </si>
+  <si>
+    <t>the, a</t>
+  </si>
+  <si>
+    <t>the, the</t>
+  </si>
+  <si>
+    <t>a, an, a</t>
+  </si>
+  <si>
+    <t>While there is life there is hope.</t>
+  </si>
+  <si>
+    <t>Her knowledge of medicine had been acquired under aged Jewess.</t>
+  </si>
+  <si>
+    <t>Her knowledge of medicine had been acquired under an aged Jewess.</t>
+  </si>
+  <si>
+    <t>Sun rises in east.</t>
+  </si>
+  <si>
+    <t>The sun rises in the east.</t>
+  </si>
+  <si>
+    <t>The brave soldier lost arm in battle.</t>
+  </si>
+  <si>
+    <t>The brave soldier lost an arm in the battle.</t>
+  </si>
+  <si>
+    <t>The doctor says it is hopeless case.</t>
+  </si>
+  <si>
+    <t>The doctor says it is a hope- less case.</t>
+  </si>
+  <si>
+    <t>I like to live in open air.</t>
+  </si>
+  <si>
+    <t>I like to live in the open air.</t>
+  </si>
+  <si>
+    <t>Get pound of sugar from nearest grocer.</t>
+  </si>
+  <si>
+    <t>Get a pound of sugar from the nearest grocer.</t>
+  </si>
+  <si>
+    <t>Set back clock; it is hour too fast.</t>
+  </si>
+  <si>
+    <t>Set back the clock; it is an hour too fast.</t>
+  </si>
+  <si>
+    <t>The poor woman has no rupee.</t>
+  </si>
+  <si>
+    <t>The poor woman has not a rupee.</t>
+  </si>
+  <si>
+    <t>You must take care.</t>
+  </si>
+  <si>
+    <t>Eskimos make houses of snow.</t>
+  </si>
+  <si>
+    <t>The Eskimos make houses of snow and ice.</t>
+  </si>
+  <si>
+    <t>Where did you buy umbrella?</t>
+  </si>
+  <si>
+    <t>Where did you buy the umbrella?</t>
+  </si>
+  <si>
+    <t>Have you never seen elephant?</t>
+  </si>
+  <si>
+    <t>Have you ever seen an elephant?</t>
+  </si>
+  <si>
+    <t>Draw map of India.</t>
+  </si>
+  <si>
+    <t>Draw the map of India.</t>
+  </si>
+  <si>
+    <t>Do not look gift horse in mouth.</t>
+  </si>
+  <si>
+    <t>Do not look a gift horse in the mouth.</t>
+  </si>
+  <si>
+    <t>Have you told him about accident?</t>
+  </si>
+  <si>
+    <t>Have you told him about the accident?</t>
+  </si>
+  <si>
+    <t>Tagore was great poet.</t>
+  </si>
+  <si>
+    <t>Tagore was a great poet.</t>
+  </si>
+  <si>
+    <t>How blue sky looks!</t>
+  </si>
+  <si>
+    <t>How blue the sky looks!</t>
+  </si>
+  <si>
+    <t>Who wishes to take walk with me?</t>
+  </si>
+  <si>
+    <t>Who wishes to take a walk with me?</t>
+  </si>
+  <si>
+    <t>What beautiful scene this is!</t>
+  </si>
+  <si>
+    <t>What a beautiful scene this is!</t>
+  </si>
+  <si>
+    <t>The musician was old Mussalman.</t>
+  </si>
+  <si>
+    <t>The musician was an old Mussalman.</t>
+  </si>
+  <si>
+    <t>river was spanned by iron bridge.</t>
+  </si>
+  <si>
+    <t>The river was spanned by an iron bridge.</t>
+  </si>
+  <si>
+    <t>Moon did not rise till after ten.</t>
+  </si>
+  <si>
+    <t>The moon did not rise till after ten.</t>
+  </si>
+  <si>
+    <t>Like true sportsmen they would give enemy fair play.</t>
+  </si>
+  <si>
+    <t>Like true sportsmen they would give the enemy fair play.</t>
+  </si>
+  <si>
+    <t>They never fail who die in great cause.</t>
+  </si>
+  <si>
+    <t>They never fail who die in a great cause.</t>
+  </si>
+  <si>
+    <t>There is nothing like staying at home for comfort.</t>
+  </si>
+  <si>
+    <t>He likes to picture himself as original thinker.</t>
+  </si>
+  <si>
+    <t>He likes to picture himself as an original thinker.</t>
+  </si>
+  <si>
+    <t>It is never thankful office to offer advice.</t>
+  </si>
+  <si>
+    <t>It is never a thankful office to offer advice.</t>
+  </si>
+  <si>
+    <t>Umbrella is of no avail against thunderstorm.</t>
+  </si>
+  <si>
+    <t>An umbrella is of no avail against the thunderstorm.</t>
+  </si>
+  <si>
+    <t>I have not seen him since he was child.</t>
+  </si>
+  <si>
+    <t>I have not seen him since he was a child.</t>
+  </si>
+  <si>
+    <t>For Brutus is honourable man.</t>
+  </si>
+  <si>
+    <t>For Brutus is an honourable man.</t>
+  </si>
+  <si>
+    <t>Neil Armstrong was first man to walk on moon.</t>
+  </si>
+  <si>
+    <t>Neil Armstrong was the first man to walk on the moon.</t>
+  </si>
+  <si>
+    <t>Man has no more right to say uncivil thing than to act one.</t>
+  </si>
+  <si>
+    <t>Man has no more right to say an uncivil thing than to act one.</t>
+  </si>
+  <si>
+    <t>We started late in afternoon.</t>
+  </si>
+  <si>
+    <t>We started late in the afternoon.</t>
+  </si>
+  <si>
+    <t>It is a strange thing how little, in general, people know about sky.</t>
+  </si>
+  <si>
+    <t>It is a strange thing how little, in general. people know about the sky.</t>
+  </si>
+  <si>
+    <t>Scheme failed for want of support.</t>
+  </si>
+  <si>
+    <t>The scheme failed for want of support.</t>
+  </si>
+  <si>
+    <t>Tiger, animal equal to lion in size, is native of Asia.</t>
+  </si>
+  <si>
+    <t>The tiger, an animal equal to the lion in size, is a native of Asia.</t>
+  </si>
+  <si>
+    <t>Time makes worst enemies friends.</t>
+  </si>
+  <si>
+    <t>Time makes the worst enemies friends.</t>
+  </si>
+  <si>
+    <t>My favourite flower is rose.</t>
+  </si>
+  <si>
+    <t>My favourite flower is the rose.</t>
+  </si>
+  <si>
+    <t>Time we live ought not to be computed by number of years, but by use that has been made of them.</t>
+  </si>
+  <si>
+    <t>The time we live ought not to be computed by the number of years, but by the use that has been made of them.</t>
+  </si>
+  <si>
+    <t>Mumbai is largest cotton textile centre in country.</t>
+  </si>
+  <si>
+    <t>Mumbai is the largest cotton textile centre in the country.</t>
+  </si>
+  <si>
+    <t>Men are too often led by astrayed- prejudice.</t>
+  </si>
+  <si>
+    <t>Men are too often led astray by prejudice.</t>
+  </si>
+  <si>
+    <t>Only best quality is sold by us.</t>
+  </si>
+  <si>
+    <t>Only the best quality is sold by us.</t>
+  </si>
+  <si>
+    <t>What kind of bird is that?</t>
+  </si>
+  <si>
+    <t>Wild animals suffer when kept in captivity.</t>
+  </si>
+  <si>
+    <t>May we have pleasure of your company?</t>
+  </si>
+  <si>
+    <t>May we have the pleasure of your company?</t>
+  </si>
+  <si>
+    <t>It was proudest moment of my life.</t>
+  </si>
+  <si>
+    <t>It was the proudest moment of my life.</t>
+  </si>
+  <si>
+    <t>Andamans are group of islands in Bay of Bengal.</t>
+  </si>
+  <si>
+    <t>The Andamans are a group of islands in the Bay of Bengal.</t>
+  </si>
+  <si>
+    <t>He started school when he was six years old.</t>
+  </si>
+  <si>
+    <t>He neglects attending church, though church is only few yards from his house.</t>
+  </si>
+  <si>
+    <t>He neglects attending church, though the church is only a few yards from his house.</t>
+  </si>
+  <si>
+    <t>March is third month of year.</t>
+  </si>
+  <si>
+    <t>March is the third month of the year.</t>
+  </si>
+  <si>
+    <t>Dr. Arnold was headmaster of Rugby.</t>
+  </si>
+  <si>
+    <t>Man cannot live by bread alone.</t>
+  </si>
+  <si>
+    <t>When will father be back?</t>
+  </si>
+  <si>
+    <t>Appenines are in Italy.</t>
+  </si>
+  <si>
+    <t>The Appenines are in Italy.</t>
   </si>
 </sst>
 </file>
@@ -8289,6 +8735,931 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:C38"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="78.28515625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="24" t="s">
+        <v>1560</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C2" t="e">
+        <f>TRIM(MID(B2,SEARCH(" ",B2,1)+1,1000))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="21" t="s">
+        <v>1563</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C3" t="e">
+        <f t="shared" ref="C3:C38" si="0">TRIM(MID(B3,SEARCH(" ",B3,1)+1,1000))</f>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="21" t="s">
+        <v>1564</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>1601</v>
+      </c>
+      <c r="C4" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="21" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C5" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="21" t="s">
+        <v>1566</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C6" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="21" t="s">
+        <v>1567</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C7" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="21" t="s">
+        <v>1568</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C8" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="21" t="s">
+        <v>1569</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C9" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="21" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C10" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="21" t="s">
+        <v>1571</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C11" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="21" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B12" s="21" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C12" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="21" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B13" s="21" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C13" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="21" t="s">
+        <v>1574</v>
+      </c>
+      <c r="B14" s="21" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C14" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="21" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B15" s="21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C15" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="21" t="s">
+        <v>1576</v>
+      </c>
+      <c r="B16" s="21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C16" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="21" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C17" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="21" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B18" s="21" t="s">
+        <v>1604</v>
+      </c>
+      <c r="C18" t="str">
+        <f t="shared" si="0"/>
+        <v>a</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="21" t="s">
+        <v>1579</v>
+      </c>
+      <c r="B19" s="21" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C19" t="str">
+        <f t="shared" si="0"/>
+        <v>the</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="21" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B20" s="21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C20" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="21" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B21" s="21" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C21" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="21" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B22" s="21" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C22" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="21" t="s">
+        <v>1583</v>
+      </c>
+      <c r="B23" s="21" t="s">
+        <v>1602</v>
+      </c>
+      <c r="C23" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="21" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B24" s="21" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C24" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="21" t="s">
+        <v>1585</v>
+      </c>
+      <c r="B25" s="21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C25" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="21" t="s">
+        <v>1586</v>
+      </c>
+      <c r="B26" s="21" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C26" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="21" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B27" s="21" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C27" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="21" t="s">
+        <v>1588</v>
+      </c>
+      <c r="B28" s="21" t="s">
+        <v>1606</v>
+      </c>
+      <c r="C28" t="str">
+        <f t="shared" si="0"/>
+        <v>an, a</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="21" t="s">
+        <v>1589</v>
+      </c>
+      <c r="B29" s="21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C29" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="21" t="s">
+        <v>1590</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>1605</v>
+      </c>
+      <c r="C30" t="str">
+        <f t="shared" si="0"/>
+        <v>the</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A31" s="21" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B31" s="21" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C31" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="21" t="s">
+        <v>1592</v>
+      </c>
+      <c r="B32" s="21" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C32" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A33" s="21" t="s">
+        <v>1593</v>
+      </c>
+      <c r="B33" s="21" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C33" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A34" s="21" t="s">
+        <v>1594</v>
+      </c>
+      <c r="B34" s="21" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C34" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A35" s="21" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B35" s="21" t="s">
+        <v>1599</v>
+      </c>
+      <c r="C35" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A36" s="21" t="s">
+        <v>1596</v>
+      </c>
+      <c r="B36" s="21" t="s">
+        <v>1603</v>
+      </c>
+      <c r="C36" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A37" s="21" t="s">
+        <v>1597</v>
+      </c>
+      <c r="B37" s="21" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C37" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A38" s="21" t="s">
+        <v>1598</v>
+      </c>
+      <c r="B38" s="21" t="s">
+        <v>1600</v>
+      </c>
+      <c r="C38" t="e">
+        <f t="shared" si="0"/>
+        <v>#VALUE!</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B56"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="50.7109375" style="32" customWidth="1"/>
+    <col min="3" max="16384" width="9.140625" style="32"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="31" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
+        <v>1607</v>
+      </c>
+      <c r="B2" s="32" t="s">
+        <v>1607</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="32" t="s">
+        <v>1608</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B4" s="32" t="s">
+        <v>1611</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="32" t="s">
+        <v>1612</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="32" t="s">
+        <v>1614</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="32" t="s">
+        <v>1616</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>1617</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="32" t="s">
+        <v>1618</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="32" t="s">
+        <v>1620</v>
+      </c>
+      <c r="B9" s="32" t="s">
+        <v>1621</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="32" t="s">
+        <v>1622</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="32" t="s">
+        <v>1624</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>1624</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="32" t="s">
+        <v>1625</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>1626</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="32" t="s">
+        <v>1627</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>1628</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="32" t="s">
+        <v>1629</v>
+      </c>
+      <c r="B14" s="32" t="s">
+        <v>1630</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="32" t="s">
+        <v>1631</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>1632</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="32" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>1634</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="32" t="s">
+        <v>1635</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>1636</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="32" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="32" t="s">
+        <v>1639</v>
+      </c>
+      <c r="B19" s="32" t="s">
+        <v>1640</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="32" t="s">
+        <v>1641</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>1642</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="32" t="s">
+        <v>1643</v>
+      </c>
+      <c r="B21" s="32" t="s">
+        <v>1644</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="32" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B22" s="32" t="s">
+        <v>1646</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" s="32" t="s">
+        <v>1647</v>
+      </c>
+      <c r="B23" s="32" t="s">
+        <v>1648</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="32" t="s">
+        <v>1649</v>
+      </c>
+      <c r="B24" s="32" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="32" t="s">
+        <v>1651</v>
+      </c>
+      <c r="B25" s="32" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" s="32" t="s">
+        <v>1653</v>
+      </c>
+      <c r="B26" s="32" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="32" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B27" s="32" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="32" t="s">
+        <v>1656</v>
+      </c>
+      <c r="B28" s="32" t="s">
+        <v>1657</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" s="32" t="s">
+        <v>1658</v>
+      </c>
+      <c r="B29" s="32" t="s">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="32" t="s">
+        <v>1660</v>
+      </c>
+      <c r="B30" s="32" t="s">
+        <v>1661</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" s="32" t="s">
+        <v>1662</v>
+      </c>
+      <c r="B31" s="32" t="s">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" s="32" t="s">
+        <v>1664</v>
+      </c>
+      <c r="B32" s="32" t="s">
+        <v>1665</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" s="32" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B33" s="32" t="s">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A34" s="32" t="s">
+        <v>1668</v>
+      </c>
+      <c r="B34" s="32" t="s">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" s="32" t="s">
+        <v>1670</v>
+      </c>
+      <c r="B35" s="32" t="s">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A36" s="32" t="s">
+        <v>1672</v>
+      </c>
+      <c r="B36" s="32" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A37" s="32" t="s">
+        <v>1674</v>
+      </c>
+      <c r="B37" s="32" t="s">
+        <v>1675</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A38" s="32" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B38" s="32" t="s">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A39" s="32" t="s">
+        <v>1678</v>
+      </c>
+      <c r="B39" s="32" t="s">
+        <v>1679</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A40" s="32" t="s">
+        <v>1680</v>
+      </c>
+      <c r="B40" s="32" t="s">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" ht="45" x14ac:dyDescent="0.25">
+      <c r="A41" s="32" t="s">
+        <v>1682</v>
+      </c>
+      <c r="B41" s="32" t="s">
+        <v>1683</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A42" s="32" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B42" s="32" t="s">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A43" s="32" t="s">
+        <v>1686</v>
+      </c>
+      <c r="B43" s="32" t="s">
+        <v>1687</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A44" s="32" t="s">
+        <v>1688</v>
+      </c>
+      <c r="B44" s="32" t="s">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A45" s="32" t="s">
+        <v>1690</v>
+      </c>
+      <c r="B45" s="32" t="s">
+        <v>1690</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A46" s="32" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B46" s="32" t="s">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A47" s="32" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B47" s="32" t="s">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A48" s="32" t="s">
+        <v>1694</v>
+      </c>
+      <c r="B48" s="32" t="s">
+        <v>1695</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" s="32" t="s">
+        <v>1696</v>
+      </c>
+      <c r="B49" s="32" t="s">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A50" s="32" t="s">
+        <v>1698</v>
+      </c>
+      <c r="B50" s="32" t="s">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" s="32" t="s">
+        <v>1699</v>
+      </c>
+      <c r="B51" s="32" t="s">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A52" s="32" t="s">
+        <v>1701</v>
+      </c>
+      <c r="B52" s="32" t="s">
+        <v>1702</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A53" s="32" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B53" s="32" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A54" s="32" t="s">
+        <v>1704</v>
+      </c>
+      <c r="B54" s="32" t="s">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A55" s="32" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B55" s="32" t="s">
+        <v>1705</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A56" s="32" t="s">
+        <v>1706</v>
+      </c>
+      <c r="B56" s="32" t="s">
+        <v>1707</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -8448,7 +9819,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -8697,7 +10068,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:C104"/>
   <sheetFormatPr defaultColWidth="62.85546875" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9541,7 +10912,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
